--- a/一覧表.xlsx
+++ b/一覧表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5da398a782259f2f/ドキュメント/Claude/Projects/演習問題/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="364" documentId="11_A9DFB6C73753FD06E80DE38136C04249F9E117FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D13A0CDA-9C5D-48AB-928F-5D8ADB89BAD8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_A9DFB6C73783FC7E50EFF49F62C14249F9E17B0B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2810" windowWidth="13430" windowHeight="7270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3550" yWindow="2490" windowWidth="13430" windowHeight="7270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="月末請求一覧" sheetId="1" r:id="rId1"/>
@@ -309,7 +309,7 @@
     <t>合計金額（請求額の合計）</t>
   </si>
   <si>
-    <t>🟨 黄色いセル（週コマ数）だけ入力してください。他の列は自動計算されるので触らなくてOKです。　📧 「Gmailを開く」で宛先・件名・請求内容まで入力済みのGmailを開けます（この内容はファイルを作った時点の金額で固定。週コマ数を変えたら一覧表.pyを再実行して作り直してください）。</t>
+    <t>🟨 黄色いセル（週コマ数）だけ入力してください。他の列は自動計算されるので触らなくてOKです。　📧 「Gmailを開く」で宛先・件名・請求内容まで入力済みのGmailを開けます（この内容はファイルを作った時点の金額で固定。週コマ数を変えたら一覧表.pyを再実行して作り直してください）。　🔽 180人分の行は普段は折りたたんであります。「合計」行の左にある［+］をクリックすると展開して週コマ数を編集できます。</t>
   </si>
   <si>
     <t>No</t>
@@ -1773,15 +1773,23 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1789,21 +1797,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1827,10 +1827,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2152,7 +2148,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O184"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2255,7 +2251,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <f t="shared" ref="A4:A35" si="0">ROW()-3</f>
         <v>1</v>
@@ -2310,7 +2306,7 @@
         <v>1：松本颯太</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -2365,7 +2361,7 @@
         <v>2：山崎咲良</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2420,7 +2416,7 @@
         <v>3：佐々木悠斗</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2475,7 +2471,7 @@
         <v>4：田中大和</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2530,7 +2526,7 @@
         <v>5：中野莉子</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2585,7 +2581,7 @@
         <v>6：橋本莉子</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2640,7 +2636,7 @@
         <v>7：佐藤駿</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2695,7 +2691,7 @@
         <v>8：阿部悠真</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2750,7 +2746,7 @@
         <v>9：石川凛</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2805,7 +2801,7 @@
         <v>10：木村美結</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2860,7 +2856,7 @@
         <v>11：小林彩花</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2915,7 +2911,7 @@
         <v>12：吉田駿</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2970,7 +2966,7 @@
         <v>13：竹内蓮</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -3025,7 +3021,7 @@
         <v>14：木村優奈</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -3080,7 +3076,7 @@
         <v>15：村上悠斗</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -3135,7 +3131,7 @@
         <v>16：石川大翔</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -3190,7 +3186,7 @@
         <v>17：太田凛</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -3245,7 +3241,7 @@
         <v>18：吉田陽向</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -3300,7 +3296,7 @@
         <v>19：山下咲良</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -3355,7 +3351,7 @@
         <v>20：後藤愛</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -3410,7 +3406,7 @@
         <v>21：田村美結</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -3465,7 +3461,7 @@
         <v>22：中野陸</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -3520,7 +3516,7 @@
         <v>23：橋本颯</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -3575,7 +3571,7 @@
         <v>24：林健太</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -3630,7 +3626,7 @@
         <v>25：金子美咲</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -3685,7 +3681,7 @@
         <v>26：山田結翔</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -3740,7 +3736,7 @@
         <v>27：田村拓也</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -3795,7 +3791,7 @@
         <v>28：田中琴音</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -3850,7 +3846,7 @@
         <v>29：近藤悠斗</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -3905,7 +3901,7 @@
         <v>30：田中遥</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -3960,7 +3956,7 @@
         <v>31：森結衣</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -4015,7 +4011,7 @@
         <v>32：松本紬</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5">
         <f t="shared" ref="A36:A67" si="6">ROW()-3</f>
         <v>33</v>
@@ -4070,7 +4066,7 @@
         <v>33：後藤翼</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5">
         <f t="shared" si="6"/>
         <v>34</v>
@@ -4125,7 +4121,7 @@
         <v>34：小野楓</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5">
         <f t="shared" si="6"/>
         <v>35</v>
@@ -4180,7 +4176,7 @@
         <v>35：山下悠斗</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5">
         <f t="shared" si="6"/>
         <v>36</v>
@@ -4235,7 +4231,7 @@
         <v>36：藤田蓮</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5">
         <f t="shared" si="6"/>
         <v>37</v>
@@ -4290,7 +4286,7 @@
         <v>37：渡辺美結</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5">
         <f t="shared" si="6"/>
         <v>38</v>
@@ -4345,7 +4341,7 @@
         <v>38：斎藤葵</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5">
         <f t="shared" si="6"/>
         <v>39</v>
@@ -4400,7 +4396,7 @@
         <v>39：岡本蒼</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A43" s="5">
         <f t="shared" si="6"/>
         <v>40</v>
@@ -4455,7 +4451,7 @@
         <v>40：小林美月</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5">
         <f t="shared" si="6"/>
         <v>41</v>
@@ -4510,7 +4506,7 @@
         <v>41：渡辺愛</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5">
         <f t="shared" si="6"/>
         <v>42</v>
@@ -4565,7 +4561,7 @@
         <v>42：高橋大翔</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A46" s="5">
         <f t="shared" si="6"/>
         <v>43</v>
@@ -4620,7 +4616,7 @@
         <v>43：田中詩織</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A47" s="5">
         <f t="shared" si="6"/>
         <v>44</v>
@@ -4675,7 +4671,7 @@
         <v>44：井上美咲</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A48" s="5">
         <f t="shared" si="6"/>
         <v>45</v>
@@ -4730,7 +4726,7 @@
         <v>45：渡辺葵</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A49" s="5">
         <f t="shared" si="6"/>
         <v>46</v>
@@ -4785,7 +4781,7 @@
         <v>46：山崎詩織</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A50" s="5">
         <f t="shared" si="6"/>
         <v>47</v>
@@ -4840,7 +4836,7 @@
         <v>47：石井心春</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A51" s="5">
         <f t="shared" si="6"/>
         <v>48</v>
@@ -4895,7 +4891,7 @@
         <v>48：佐藤健太</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A52" s="5">
         <f t="shared" si="6"/>
         <v>49</v>
@@ -4950,7 +4946,7 @@
         <v>49：石井結衣</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A53" s="5">
         <f t="shared" si="6"/>
         <v>50</v>
@@ -5005,7 +5001,7 @@
         <v>50：小川心春</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A54" s="5">
         <f t="shared" si="6"/>
         <v>51</v>
@@ -5060,7 +5056,7 @@
         <v>51：青木彩花</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A55" s="5">
         <f t="shared" si="6"/>
         <v>52</v>
@@ -5115,7 +5111,7 @@
         <v>52：福田蓮</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A56" s="5">
         <f t="shared" si="6"/>
         <v>53</v>
@@ -5170,7 +5166,7 @@
         <v>53：伊藤大輝</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A57" s="5">
         <f t="shared" si="6"/>
         <v>54</v>
@@ -5225,7 +5221,7 @@
         <v>54：山下優奈</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <f t="shared" si="6"/>
         <v>55</v>
@@ -5280,7 +5276,7 @@
         <v>55：橋本蓮</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <f t="shared" si="6"/>
         <v>56</v>
@@ -5335,7 +5331,7 @@
         <v>56：遠藤彩花</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <f t="shared" si="6"/>
         <v>57</v>
@@ -5390,7 +5386,7 @@
         <v>57：林一輝</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <f t="shared" si="6"/>
         <v>58</v>
@@ -5445,7 +5441,7 @@
         <v>58：小野咲良</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A62" s="5">
         <f t="shared" si="6"/>
         <v>59</v>
@@ -5500,7 +5496,7 @@
         <v>59：後藤紬</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A63" s="5">
         <f t="shared" si="6"/>
         <v>60</v>
@@ -5555,7 +5551,7 @@
         <v>60：小林颯太</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A64" s="5">
         <f t="shared" si="6"/>
         <v>61</v>
@@ -5610,7 +5606,7 @@
         <v>61：伊藤駿</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A65" s="5">
         <f t="shared" si="6"/>
         <v>62</v>
@@ -5665,7 +5661,7 @@
         <v>62：山下大和</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A66" s="5">
         <f t="shared" si="6"/>
         <v>63</v>
@@ -5720,7 +5716,7 @@
         <v>63：後藤翔太</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A67" s="5">
         <f t="shared" si="6"/>
         <v>64</v>
@@ -5775,7 +5771,7 @@
         <v>64：鈴木結衣</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A68" s="5">
         <f t="shared" ref="A68:A99" si="12">ROW()-3</f>
         <v>65</v>
@@ -5830,7 +5826,7 @@
         <v>65：中野一輝</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A69" s="5">
         <f t="shared" si="12"/>
         <v>66</v>
@@ -5885,7 +5881,7 @@
         <v>66：後藤湊</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A70" s="5">
         <f t="shared" si="12"/>
         <v>67</v>
@@ -5940,7 +5936,7 @@
         <v>67：佐々木さくら</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A71" s="5">
         <f t="shared" si="12"/>
         <v>68</v>
@@ -5995,7 +5991,7 @@
         <v>68：松本拓也</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A72" s="5">
         <f t="shared" si="12"/>
         <v>69</v>
@@ -6050,7 +6046,7 @@
         <v>69：高橋陽菜</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A73" s="5">
         <f t="shared" si="12"/>
         <v>70</v>
@@ -6105,7 +6101,7 @@
         <v>70：青木湊</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A74" s="5">
         <f t="shared" si="12"/>
         <v>71</v>
@@ -6160,7 +6156,7 @@
         <v>71：鈴木琴音</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A75" s="5">
         <f t="shared" si="12"/>
         <v>72</v>
@@ -6215,7 +6211,7 @@
         <v>72：岡本彩花</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A76" s="5">
         <f t="shared" si="12"/>
         <v>73</v>
@@ -6270,7 +6266,7 @@
         <v>73：井上蓮</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A77" s="5">
         <f t="shared" si="12"/>
         <v>74</v>
@@ -6325,7 +6321,7 @@
         <v>74：加藤一輝</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A78" s="5">
         <f t="shared" si="12"/>
         <v>75</v>
@@ -6380,7 +6376,7 @@
         <v>75：渡辺煌</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A79" s="5">
         <f t="shared" si="12"/>
         <v>76</v>
@@ -6435,7 +6431,7 @@
         <v>76：小川美月</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A80" s="5">
         <f t="shared" si="12"/>
         <v>77</v>
@@ -6490,7 +6486,7 @@
         <v>77：岡本陽向</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A81" s="5">
         <f t="shared" si="12"/>
         <v>78</v>
@@ -6545,7 +6541,7 @@
         <v>78：小川陽向</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A82" s="5">
         <f t="shared" si="12"/>
         <v>79</v>
@@ -6600,7 +6596,7 @@
         <v>79：田中結衣</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A83" s="5">
         <f t="shared" si="12"/>
         <v>80</v>
@@ -6655,7 +6651,7 @@
         <v>80：橋本煌</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A84" s="5">
         <f t="shared" si="12"/>
         <v>81</v>
@@ -6710,7 +6706,7 @@
         <v>81：松本萌</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A85" s="5">
         <f t="shared" si="12"/>
         <v>82</v>
@@ -6765,7 +6761,7 @@
         <v>82：小野結衣</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A86" s="5">
         <f t="shared" si="12"/>
         <v>83</v>
@@ -6820,7 +6816,7 @@
         <v>83：藤井陽向</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A87" s="5">
         <f t="shared" si="12"/>
         <v>84</v>
@@ -6875,7 +6871,7 @@
         <v>84：村上尊</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A88" s="5">
         <f t="shared" si="12"/>
         <v>85</v>
@@ -6930,7 +6926,7 @@
         <v>85：山田花音</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A89" s="5">
         <f t="shared" si="12"/>
         <v>86</v>
@@ -6985,7 +6981,7 @@
         <v>86：小川駿</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A90" s="5">
         <f t="shared" si="12"/>
         <v>87</v>
@@ -7040,7 +7036,7 @@
         <v>87：中野健太</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A91" s="5">
         <f t="shared" si="12"/>
         <v>88</v>
@@ -7095,7 +7091,7 @@
         <v>88：田中結翔</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A92" s="5">
         <f t="shared" si="12"/>
         <v>89</v>
@@ -7150,7 +7146,7 @@
         <v>89：伊藤翼</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A93" s="5">
         <f t="shared" si="12"/>
         <v>90</v>
@@ -7205,7 +7201,7 @@
         <v>90：後藤颯太</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A94" s="5">
         <f t="shared" si="12"/>
         <v>91</v>
@@ -7260,7 +7256,7 @@
         <v>91：井上大和</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A95" s="5">
         <f t="shared" si="12"/>
         <v>92</v>
@@ -7315,7 +7311,7 @@
         <v>92：井上詩織</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A96" s="5">
         <f t="shared" si="12"/>
         <v>93</v>
@@ -7370,7 +7366,7 @@
         <v>93：中島琴音</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A97" s="5">
         <f t="shared" si="12"/>
         <v>94</v>
@@ -7425,7 +7421,7 @@
         <v>94：山本拓也</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A98" s="5">
         <f t="shared" si="12"/>
         <v>95</v>
@@ -7480,7 +7476,7 @@
         <v>95：池田颯</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A99" s="5">
         <f t="shared" si="12"/>
         <v>96</v>
@@ -7535,7 +7531,7 @@
         <v>96：斎藤彩花</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A100" s="5">
         <f t="shared" ref="A100:A131" si="18">ROW()-3</f>
         <v>97</v>
@@ -7590,7 +7586,7 @@
         <v>97：山本愛</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A101" s="5">
         <f t="shared" si="18"/>
         <v>98</v>
@@ -7645,7 +7641,7 @@
         <v>98：小野美咲</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A102" s="5">
         <f t="shared" si="18"/>
         <v>99</v>
@@ -7700,7 +7696,7 @@
         <v>99：石川美咲</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A103" s="5">
         <f t="shared" si="18"/>
         <v>100</v>
@@ -7755,7 +7751,7 @@
         <v>100：阿部拓也</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A104" s="5">
         <f t="shared" si="18"/>
         <v>101</v>
@@ -7810,7 +7806,7 @@
         <v>101：西村彩花</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A105" s="5">
         <f t="shared" si="18"/>
         <v>102</v>
@@ -7865,7 +7861,7 @@
         <v>102：森健太</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A106" s="5">
         <f t="shared" si="18"/>
         <v>103</v>
@@ -7920,7 +7916,7 @@
         <v>103：伊藤悠真</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A107" s="5">
         <f t="shared" si="18"/>
         <v>104</v>
@@ -7975,7 +7971,7 @@
         <v>104：松本大輝</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A108" s="5">
         <f t="shared" si="18"/>
         <v>105</v>
@@ -8030,7 +8026,7 @@
         <v>105：太田拓也</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A109" s="5">
         <f t="shared" si="18"/>
         <v>106</v>
@@ -8085,7 +8081,7 @@
         <v>106：中島悠真</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A110" s="5">
         <f t="shared" si="18"/>
         <v>107</v>
@@ -8140,7 +8136,7 @@
         <v>107：中野咲良</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A111" s="5">
         <f t="shared" si="18"/>
         <v>108</v>
@@ -8195,7 +8191,7 @@
         <v>108：吉田優奈</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A112" s="5">
         <f t="shared" si="18"/>
         <v>109</v>
@@ -8250,7 +8246,7 @@
         <v>109：林大翔</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A113" s="5">
         <f t="shared" si="18"/>
         <v>110</v>
@@ -8305,7 +8301,7 @@
         <v>110：青木陽菜</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A114" s="5">
         <f t="shared" si="18"/>
         <v>111</v>
@@ -8360,7 +8356,7 @@
         <v>111：清水一輝</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A115" s="5">
         <f t="shared" si="18"/>
         <v>112</v>
@@ -8415,7 +8411,7 @@
         <v>112：井上朝陽</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A116" s="5">
         <f t="shared" si="18"/>
         <v>113</v>
@@ -8470,7 +8466,7 @@
         <v>113：中野美桜</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A117" s="5">
         <f t="shared" si="18"/>
         <v>114</v>
@@ -8525,7 +8521,7 @@
         <v>114：林美月</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A118" s="5">
         <f t="shared" si="18"/>
         <v>115</v>
@@ -8580,7 +8576,7 @@
         <v>115：加藤悠斗</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A119" s="5">
         <f t="shared" si="18"/>
         <v>116</v>
@@ -8635,7 +8631,7 @@
         <v>116：福田結衣</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A120" s="5">
         <f t="shared" si="18"/>
         <v>117</v>
@@ -8690,7 +8686,7 @@
         <v>117：山口陽向</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A121" s="5">
         <f t="shared" si="18"/>
         <v>118</v>
@@ -8745,7 +8741,7 @@
         <v>118：高橋蒼</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A122" s="5">
         <f t="shared" si="18"/>
         <v>119</v>
@@ -8800,7 +8796,7 @@
         <v>119：林翔太</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A123" s="5">
         <f t="shared" si="18"/>
         <v>120</v>
@@ -8855,7 +8851,7 @@
         <v>120：岡田詩織</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A124" s="5">
         <f t="shared" si="18"/>
         <v>121</v>
@@ -8910,7 +8906,7 @@
         <v>121：後藤蒼</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A125" s="5">
         <f t="shared" si="18"/>
         <v>122</v>
@@ -8965,7 +8961,7 @@
         <v>122：渡辺陽菜乃</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A126" s="5">
         <f t="shared" si="18"/>
         <v>123</v>
@@ -9020,7 +9016,7 @@
         <v>123：小川一輝</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A127" s="5">
         <f t="shared" si="18"/>
         <v>124</v>
@@ -9075,7 +9071,7 @@
         <v>124：斎藤愛</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A128" s="5">
         <f t="shared" si="18"/>
         <v>125</v>
@@ -9130,7 +9126,7 @@
         <v>125：長谷川咲良</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A129" s="5">
         <f t="shared" si="18"/>
         <v>126</v>
@@ -9185,7 +9181,7 @@
         <v>126：長谷川煌</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A130" s="5">
         <f t="shared" si="18"/>
         <v>127</v>
@@ -9240,7 +9236,7 @@
         <v>127：吉田萌</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A131" s="5">
         <f t="shared" si="18"/>
         <v>128</v>
@@ -9295,7 +9291,7 @@
         <v>128：山本一輝</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A132" s="5">
         <f t="shared" ref="A132:A163" si="24">ROW()-3</f>
         <v>129</v>
@@ -9350,7 +9346,7 @@
         <v>129：坂本凛</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A133" s="5">
         <f t="shared" si="24"/>
         <v>130</v>
@@ -9405,7 +9401,7 @@
         <v>130：佐藤蒼</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A134" s="5">
         <f t="shared" si="24"/>
         <v>131</v>
@@ -9460,7 +9456,7 @@
         <v>131：前田結翔</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A135" s="5">
         <f t="shared" si="24"/>
         <v>132</v>
@@ -9515,7 +9511,7 @@
         <v>132：竹内蒼</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A136" s="5">
         <f t="shared" si="24"/>
         <v>133</v>
@@ -9570,7 +9566,7 @@
         <v>133：加藤葵</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A137" s="5">
         <f t="shared" si="24"/>
         <v>134</v>
@@ -9625,7 +9621,7 @@
         <v>134：佐藤萌</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A138" s="5">
         <f t="shared" si="24"/>
         <v>135</v>
@@ -9680,7 +9676,7 @@
         <v>135：阿部花音</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A139" s="5">
         <f t="shared" si="24"/>
         <v>136</v>
@@ -9735,7 +9731,7 @@
         <v>136：近藤大和</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A140" s="5">
         <f t="shared" si="24"/>
         <v>137</v>
@@ -9790,7 +9786,7 @@
         <v>137：田村陽向</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A141" s="5">
         <f t="shared" si="24"/>
         <v>138</v>
@@ -9845,7 +9841,7 @@
         <v>138：岡本美結</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A142" s="5">
         <f t="shared" si="24"/>
         <v>139</v>
@@ -9900,7 +9896,7 @@
         <v>139：森花音</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A143" s="5">
         <f t="shared" si="24"/>
         <v>140</v>
@@ -9955,7 +9951,7 @@
         <v>140：太田優奈</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A144" s="5">
         <f t="shared" si="24"/>
         <v>141</v>
@@ -10010,7 +10006,7 @@
         <v>141：山本美月</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A145" s="5">
         <f t="shared" si="24"/>
         <v>142</v>
@@ -10065,7 +10061,7 @@
         <v>142：木村心春</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A146" s="5">
         <f t="shared" si="24"/>
         <v>143</v>
@@ -10120,7 +10116,7 @@
         <v>143：山口朝陽</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A147" s="5">
         <f t="shared" si="24"/>
         <v>144</v>
@@ -10175,7 +10171,7 @@
         <v>144：伊藤楓</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A148" s="5">
         <f t="shared" si="24"/>
         <v>145</v>
@@ -10230,7 +10226,7 @@
         <v>145：斎藤一輝</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A149" s="5">
         <f t="shared" si="24"/>
         <v>146</v>
@@ -10285,7 +10281,7 @@
         <v>146：遠藤大和</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A150" s="5">
         <f t="shared" si="24"/>
         <v>147</v>
@@ -10340,7 +10336,7 @@
         <v>147：金子心春</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A151" s="5">
         <f t="shared" si="24"/>
         <v>148</v>
@@ -10395,7 +10391,7 @@
         <v>148：田中美桜</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A152" s="5">
         <f t="shared" si="24"/>
         <v>149</v>
@@ -10450,7 +10446,7 @@
         <v>149：小野湊</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A153" s="5">
         <f t="shared" si="24"/>
         <v>150</v>
@@ -10505,7 +10501,7 @@
         <v>150：石井琴音</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A154" s="5">
         <f t="shared" si="24"/>
         <v>151</v>
@@ -10560,7 +10556,7 @@
         <v>151：近藤大翔</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A155" s="5">
         <f t="shared" si="24"/>
         <v>152</v>
@@ -10615,7 +10611,7 @@
         <v>152：佐藤悠真</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A156" s="5">
         <f t="shared" si="24"/>
         <v>153</v>
@@ -10670,7 +10666,7 @@
         <v>153：長谷川美月</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A157" s="5">
         <f t="shared" si="24"/>
         <v>154</v>
@@ -10725,7 +10721,7 @@
         <v>154：近藤拓也</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A158" s="5">
         <f t="shared" si="24"/>
         <v>155</v>
@@ -10780,7 +10776,7 @@
         <v>155：中村駿</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A159" s="5">
         <f t="shared" si="24"/>
         <v>156</v>
@@ -10835,7 +10831,7 @@
         <v>156：伊藤煌</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A160" s="5">
         <f t="shared" si="24"/>
         <v>157</v>
@@ -10890,7 +10886,7 @@
         <v>157：金子美桜</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A161" s="5">
         <f t="shared" si="24"/>
         <v>158</v>
@@ -10945,7 +10941,7 @@
         <v>158：池田彩花</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A162" s="5">
         <f t="shared" si="24"/>
         <v>159</v>
@@ -11000,7 +10996,7 @@
         <v>159：岡本悠斗</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A163" s="5">
         <f t="shared" si="24"/>
         <v>160</v>
@@ -11055,7 +11051,7 @@
         <v>160：加藤湊</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A164" s="5">
         <f t="shared" ref="A164:A183" si="30">ROW()-3</f>
         <v>161</v>
@@ -11080,7 +11076,7 @@
         <v>3</v>
       </c>
       <c r="H164" s="8">
-        <f t="shared" ref="H164:H183" si="31">G164*4</f>
+        <f t="shared" ref="H164:H195" si="31">G164*4</f>
         <v>12</v>
       </c>
       <c r="I164" s="6">
@@ -11092,7 +11088,7 @@
         <v>25200</v>
       </c>
       <c r="K164" s="6">
-        <f t="shared" ref="K164:K183" si="33">J164+I164+ROUND((J164+I164)*0.1,0)</f>
+        <f t="shared" ref="K164:K195" si="33">J164+I164+ROUND((J164+I164)*0.1,0)</f>
         <v>31020</v>
       </c>
       <c r="L164" t="s">
@@ -11110,7 +11106,7 @@
         <v>161：松本結翔</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A165" s="5">
         <f t="shared" si="30"/>
         <v>162</v>
@@ -11165,7 +11161,7 @@
         <v>162：山崎美咲</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A166" s="5">
         <f t="shared" si="30"/>
         <v>163</v>
@@ -11220,7 +11216,7 @@
         <v>163：山口大翔</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A167" s="5">
         <f t="shared" si="30"/>
         <v>164</v>
@@ -11275,7 +11271,7 @@
         <v>164：鈴木遥</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A168" s="5">
         <f t="shared" si="30"/>
         <v>165</v>
@@ -11330,7 +11326,7 @@
         <v>165：小野朝陽</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A169" s="5">
         <f t="shared" si="30"/>
         <v>166</v>
@@ -11385,7 +11381,7 @@
         <v>166：山崎紬</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A170" s="5">
         <f t="shared" si="30"/>
         <v>167</v>
@@ -11440,7 +11436,7 @@
         <v>167：岡田葵</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A171" s="5">
         <f t="shared" si="30"/>
         <v>168</v>
@@ -11495,7 +11491,7 @@
         <v>168：田村琴音</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A172" s="5">
         <f t="shared" si="30"/>
         <v>169</v>
@@ -11550,7 +11546,7 @@
         <v>169：竹内楓</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A173" s="5">
         <f t="shared" si="30"/>
         <v>170</v>
@@ -11605,7 +11601,7 @@
         <v>170：藤井遥</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A174" s="5">
         <f t="shared" si="30"/>
         <v>171</v>
@@ -11660,7 +11656,7 @@
         <v>171：長谷川悠真</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A175" s="5">
         <f t="shared" si="30"/>
         <v>172</v>
@@ -11715,7 +11711,7 @@
         <v>172：林海斗</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A176" s="5">
         <f t="shared" si="30"/>
         <v>173</v>
@@ -11770,7 +11766,7 @@
         <v>173：伊藤萌</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A177" s="5">
         <f t="shared" si="30"/>
         <v>174</v>
@@ -11825,7 +11821,7 @@
         <v>174：近藤蓮</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A178" s="5">
         <f t="shared" si="30"/>
         <v>175</v>
@@ -11880,7 +11876,7 @@
         <v>175：井上尊</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A179" s="5">
         <f t="shared" si="30"/>
         <v>176</v>
@@ -11935,7 +11931,7 @@
         <v>176：西村尊</v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A180" s="5">
         <f t="shared" si="30"/>
         <v>177</v>
@@ -11990,7 +11986,7 @@
         <v>177：藤井美桜</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A181" s="5">
         <f t="shared" si="30"/>
         <v>178</v>
@@ -12045,7 +12041,7 @@
         <v>178：山口美桜</v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A182" s="5">
         <f t="shared" si="30"/>
         <v>179</v>
@@ -12100,7 +12096,7 @@
         <v>179：竹内花音</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A183" s="5">
         <f t="shared" si="30"/>
         <v>180</v>
@@ -12155,7 +12151,7 @@
         <v>180：前田葵</v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:15" collapsed="1" x14ac:dyDescent="0.2">
       <c r="A184" s="45" t="s">
         <v>428</v>
       </c>
@@ -12407,7 +12403,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.4">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="23"/>
@@ -12415,19 +12411,19 @@
       <c r="D1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="27">
+      <c r="E1" s="34">
         <f ca="1">TODAY()</f>
         <v>46252</v>
       </c>
       <c r="F1" s="23"/>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="28" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="23"/>
       <c r="J1" s="23"/>
       <c r="K1" s="23"/>
       <c r="L1" s="23"/>
-      <c r="N1" s="39" t="s">
+      <c r="N1" s="29" t="s">
         <v>3</v>
       </c>
       <c r="O1" s="23"/>
@@ -12440,7 +12436,7 @@
       <c r="D2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="35" t="str">
+      <c r="E2" s="40" t="str">
         <f>IFERROR(INDEX(SeikyuData[No],MATCH($J$6,SeikyuData[No],0)),"")</f>
         <v/>
       </c>
@@ -12448,27 +12444,27 @@
       <c r="H2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="40" t="s">
+      <c r="N2" s="25" t="s">
         <v>7</v>
       </c>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="H3" s="44" t="s">
+      <c r="H3" s="27" t="s">
         <v>8</v>
       </c>
       <c r="I3" s="23"/>
       <c r="J3" s="23"/>
       <c r="K3" s="23"/>
-      <c r="N3" s="22" t="s">
+      <c r="N3" s="32" t="s">
         <v>9</v>
       </c>
       <c r="O3" s="23"/>
       <c r="P3" s="23"/>
     </row>
     <row r="4" spans="1:16" ht="19" x14ac:dyDescent="0.3">
-      <c r="A4" s="31" t="str">
+      <c r="A4" s="37" t="str">
         <f>IF($J$6="","（右の操作パネルでNoか生徒名を選択してください）",$J$7&amp;"　様")</f>
         <v>（右の操作パネルでNoか生徒名を選択してください）</v>
       </c>
@@ -12480,14 +12476,14 @@
       <c r="H4" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="33"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="39"/>
       <c r="N4" s="23"/>
       <c r="O4" s="23"/>
       <c r="P4" s="23"/>
     </row>
     <row r="5" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="30" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="23"/>
@@ -12498,9 +12494,9 @@
       <c r="H5" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="36"/>
-      <c r="K5" s="37"/>
-      <c r="L5" s="33"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="39"/>
     </row>
     <row r="6" spans="1:16" ht="15.5" x14ac:dyDescent="0.25">
       <c r="H6" s="16" t="s">
@@ -12585,13 +12581,13 @@
       <c r="A11" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="25" t="str">
+      <c r="C11" s="22" t="str">
         <f>IFERROR(INDEX(SeikyuData[1コマ単価],MATCH($J$6,SeikyuData[No],0)),"")</f>
         <v/>
       </c>
       <c r="D11" s="23"/>
       <c r="E11" s="23"/>
-      <c r="J11" s="40" t="str">
+      <c r="J11" s="25" t="str">
         <f>IF($J$6="","",HYPERLINK("https://mail.google.com/mail/?view=cm&amp;fs=1&amp;to=" &amp; _xlfn.ENCODEURL(IFERROR(INDEX(SeikyuData[保護者メール],MATCH($J$6,SeikyuData[No],0)),"")) &amp; "&amp;su=" &amp; _xlfn.ENCODEURL($J$7 &amp; "様 2026年8月分請求のお知らせ"),"📧 Gmail作成画面を開く（宛先・件名 入力済み）"))</f>
         <v/>
       </c>
@@ -12602,13 +12598,13 @@
       <c r="A12" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="34" t="str">
+      <c r="C12" s="31" t="str">
         <f>IFERROR(INDEX(SeikyuData[週コマ数],MATCH($J$6,SeikyuData[No],0)),"")</f>
         <v/>
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
-      <c r="J12" s="22" t="s">
+      <c r="J12" s="32" t="s">
         <v>24</v>
       </c>
       <c r="K12" s="23"/>
@@ -12618,7 +12614,7 @@
       <c r="A13" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="34" t="str">
+      <c r="C13" s="31" t="str">
         <f>IFERROR(INDEX(SeikyuData[コマ数],MATCH($J$6,SeikyuData[No],0)),"")</f>
         <v/>
       </c>
@@ -12629,7 +12625,7 @@
       <c r="A14" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="25" t="str">
+      <c r="C14" s="22" t="str">
         <f>IFERROR(INDEX(SeikyuData[教材費],MATCH($J$6,SeikyuData[No],0)),"")</f>
         <v/>
       </c>
@@ -12643,13 +12639,13 @@
       <c r="A15" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="25" t="str">
+      <c r="C15" s="22" t="str">
         <f>IFERROR(INDEX(SeikyuData[授業料],MATCH($J$6,SeikyuData[No],0)),"")</f>
         <v/>
       </c>
       <c r="D15" s="23"/>
       <c r="E15" s="23"/>
-      <c r="H15" s="43" t="str">
+      <c r="H15" s="26" t="str">
         <f ca="1">IF($J$6="","生徒名を選択すると本文が生成されます。",$J$7&amp;"様"&amp;CHAR(10)&amp;CHAR(10)&amp;"いつもお世話になっております。さくら学習塾です。"&amp;CHAR(10)&amp;"2026年8月分の請求内容は以下の通りです。"&amp;CHAR(10)&amp;CHAR(10)&amp;"教室：　"&amp;IFERROR(INDEX(SeikyuData[教室],MATCH($J$6,SeikyuData[No],0)),"")&amp;CHAR(10)&amp;"コース：　"&amp;IFERROR(INDEX(SeikyuData[コース],MATCH($J$6,SeikyuData[No],0)),"")&amp;CHAR(10)&amp;"コマ数：　"&amp;IFERROR(INDEX(SeikyuData[コマ数],MATCH($J$6,SeikyuData[No],0)),"")&amp;"コマ"&amp;CHAR(10)&amp;"授業料：　"&amp;TEXT(IFERROR(INDEX(SeikyuData[授業料],MATCH($J$6,SeikyuData[No],0)),""),"#,##0")&amp;"円"&amp;CHAR(10)&amp;"教材費：　"&amp;TEXT(IFERROR(INDEX(SeikyuData[教材費],MATCH($J$6,SeikyuData[No],0)),""),"#,##0")&amp;"円"&amp;CHAR(10)&amp;"消費税：　"&amp;TEXT(ROUND((IFERROR(INDEX(SeikyuData[授業料],MATCH($J$6,SeikyuData[No],0)),"")+IFERROR(INDEX(SeikyuData[教材費],MATCH($J$6,SeikyuData[No],0)),""))*0.1,0),"#,##0")&amp;"円"&amp;CHAR(10)&amp;"----------------"&amp;CHAR(10)&amp;"ご請求額：　"&amp;TEXT(IFERROR(INDEX(SeikyuData[請求額(税込)],MATCH($J$6,SeikyuData[No],0)),""),"#,##0")&amp;"円"&amp;CHAR(10)&amp;CHAR(10)&amp;"振込先：　〇〇銀行 〇〇支店　普通　1234567　口座名義：サクラガクシュウジュク"&amp;CHAR(10)&amp;"支払期日：　"&amp;TEXT(TODAY()+14,"yyyy/mm/dd")&amp;CHAR(10)&amp;CHAR(10)&amp;"お手数ですが、期日までにお振込みくださいますようお願いいたします。")</f>
         <v>生徒名を選択すると本文が生成されます。</v>
       </c>
@@ -12662,7 +12658,7 @@
       <c r="A16" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="25" t="str">
+      <c r="C16" s="22" t="str">
         <f>IFERROR(ROUND((INDEX(SeikyuData[授業料],MATCH($J$6,SeikyuData[No],0))+INDEX(SeikyuData[教材費],MATCH($J$6,SeikyuData[No],0)))*0.1,0),"")</f>
         <v/>
       </c>
@@ -12679,12 +12675,12 @@
         <v>30</v>
       </c>
       <c r="B17" s="2"/>
-      <c r="C17" s="29" t="str">
+      <c r="C17" s="35" t="str">
         <f>IFERROR(INDEX(SeikyuData[請求額(税込)],MATCH($J$6,SeikyuData[No],0)),"")</f>
         <v/>
       </c>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
       <c r="F17" s="2"/>
       <c r="H17" s="23"/>
       <c r="I17" s="23"/>
@@ -12703,7 +12699,7 @@
       <c r="A19" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="30" t="s">
         <v>32</v>
       </c>
       <c r="C19" s="23"/>
@@ -12720,7 +12716,7 @@
       <c r="A20" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="42">
+      <c r="B20" s="44">
         <f ca="1">TODAY()+14</f>
         <v>46266</v>
       </c>
@@ -12735,7 +12731,7 @@
       <c r="L20" s="23"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="30" t="s">
         <v>34</v>
       </c>
       <c r="B21" s="23"/>
@@ -12823,14 +12819,14 @@
       <c r="L30" s="23"/>
     </row>
     <row r="32" spans="1:12" ht="14" x14ac:dyDescent="0.2">
-      <c r="J32" s="26" t="s">
+      <c r="J32" s="33" t="s">
         <v>38</v>
       </c>
       <c r="K32" s="23"/>
       <c r="L32" s="23"/>
     </row>
     <row r="33" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J33" s="22" t="s">
+      <c r="J33" s="32" t="s">
         <v>39</v>
       </c>
       <c r="K33" s="23"/>
@@ -12898,9 +12894,22 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="H3:K3"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="J33:L34"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="J32:L32"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="J5:L5"/>
     <mergeCell ref="H1:L1"/>
     <mergeCell ref="N1:P1"/>
     <mergeCell ref="A21:F21"/>
@@ -12917,22 +12926,9 @@
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="H15:L30"/>
-    <mergeCell ref="J33:L34"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="J32:L32"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="E23:F23"/>
   </mergeCells>
   <phoneticPr fontId="22"/>
   <hyperlinks>
@@ -12940,10 +12936,10 @@
     <hyperlink ref="H3" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
-  <legacyDrawing r:id="rId4"/>
+  <pageSetup orientation="portrait"/>
+  <legacyDrawing r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">

--- a/一覧表.xlsx
+++ b/一覧表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5da398a782259f2f/ドキュメント/Claude/Projects/演習問題/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_A9DFB6C73783FC7E50EFF49F62C14249F9E17B0B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_8E1FB7C76C0B3F77EAAFFC8136C04249F91CF42A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3550" yWindow="2490" windowWidth="13430" windowHeight="7270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -169,7 +169,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="432">
   <si>
     <t>請求書</t>
   </si>
@@ -210,15 +210,24 @@
     <t>② または生徒名で選択 ▶</t>
   </si>
   <si>
+    <t>🔧 週コマ数を変えるときは</t>
+  </si>
+  <si>
     <t>選択中のNo</t>
   </si>
   <si>
+    <t>📋 一覧表を開く（週コマ数を編集）</t>
+  </si>
+  <si>
     <t>ご請求内容</t>
   </si>
   <si>
     <t>選択中の生徒名</t>
   </si>
   <si>
+    <t>「月末請求一覧」タブに切り替わります。黄色いセル（週コマ数）に数字を入力してください。</t>
+  </si>
+  <si>
     <t>教室</t>
   </si>
   <si>
@@ -309,7 +318,7 @@
     <t>合計金額（請求額の合計）</t>
   </si>
   <si>
-    <t>🟨 黄色いセル（週コマ数）だけ入力してください。他の列は自動計算されるので触らなくてOKです。　📧 「Gmailを開く」で宛先・件名・請求内容まで入力済みのGmailを開けます（この内容はファイルを作った時点の金額で固定。週コマ数を変えたら一覧表.pyを再実行して作り直してください）。　🔽 180人分の行は普段は折りたたんであります。「合計」行の左にある［+］をクリックすると展開して週コマ数を編集できます。</t>
+    <t>🟨 黄色いセル（週コマ数）だけ入力してください。他の列は自動計算されるので触らなくてOKです。　📧 「Gmailを開く」で宛先・件名・請求内容まで入力済みのGmailを開けます（この内容はファイルを作った時点の金額で固定。週コマ数を変えたら一覧表.pyを再実行して作り直してください）。</t>
   </si>
   <si>
     <t>No</t>
@@ -1781,8 +1790,8 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2148,7 +2157,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O184"/>
-  <sheetFormatPr defaultRowHeight="13" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2169,7 +2178,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B1" s="47">
         <f>SUM(SeikyuData[請求額(税込)])</f>
@@ -2188,7 +2197,7 @@
     </row>
     <row r="2" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="48" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
@@ -2206,67 +2215,67 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <f t="shared" ref="A4:A35" si="0">ROW()-3</f>
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F4" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E4,TankaData[コース],0)),0)</f>
@@ -2292,10 +2301,10 @@
         <v>52800</v>
       </c>
       <c r="L4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N4" s="10" t="str">
         <f t="shared" ref="N4:N35" si="4">"教室："&amp;C4&amp;"／コース："&amp;E4&amp;"／コマ数："&amp;H4&amp;"コマ／授業料："&amp;TEXT(J4,"#,##0")&amp;"円／教材費："&amp;TEXT(I4,"#,##0")&amp;"円／消費税："&amp;TEXT(ROUND((J4+I4)*0.1,0),"#,##0")&amp;"円／請求額："&amp;TEXT(K4,"#,##0")&amp;"円"</f>
@@ -2306,22 +2315,22 @@
         <v>1：松本颯太</v>
       </c>
     </row>
-    <row r="5" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F5" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E5,TankaData[コース],0)),0)</f>
@@ -2347,10 +2356,10 @@
         <v>60500</v>
       </c>
       <c r="L5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N5" s="10" t="str">
         <f t="shared" si="4"/>
@@ -2361,22 +2370,22 @@
         <v>2：山崎咲良</v>
       </c>
     </row>
-    <row r="6" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F6" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E6,TankaData[コース],0)),0)</f>
@@ -2402,10 +2411,10 @@
         <v>60500</v>
       </c>
       <c r="L6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N6" s="10" t="str">
         <f t="shared" si="4"/>
@@ -2416,22 +2425,22 @@
         <v>3：佐々木悠斗</v>
       </c>
     </row>
-    <row r="7" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F7" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E7,TankaData[コース],0)),0)</f>
@@ -2457,10 +2466,10 @@
         <v>48950</v>
       </c>
       <c r="L7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N7" s="10" t="str">
         <f t="shared" si="4"/>
@@ -2471,22 +2480,22 @@
         <v>4：田中大和</v>
       </c>
     </row>
-    <row r="8" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F8" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E8,TankaData[コース],0)),0)</f>
@@ -2512,10 +2521,10 @@
         <v>31020</v>
       </c>
       <c r="L8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N8" s="10" t="str">
         <f t="shared" si="4"/>
@@ -2526,22 +2535,22 @@
         <v>5：中野莉子</v>
       </c>
     </row>
-    <row r="9" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F9" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E9,TankaData[コース],0)),0)</f>
@@ -2567,10 +2576,10 @@
         <v>37400</v>
       </c>
       <c r="L9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N9" s="10" t="str">
         <f t="shared" si="4"/>
@@ -2581,22 +2590,22 @@
         <v>6：橋本莉子</v>
       </c>
     </row>
-    <row r="10" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F10" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E10,TankaData[コース],0)),0)</f>
@@ -2622,10 +2631,10 @@
         <v>21780</v>
       </c>
       <c r="L10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N10" s="10" t="str">
         <f t="shared" si="4"/>
@@ -2636,22 +2645,22 @@
         <v>7：佐藤駿</v>
       </c>
     </row>
-    <row r="11" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F11" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E11,TankaData[コース],0)),0)</f>
@@ -2677,10 +2686,10 @@
         <v>49500</v>
       </c>
       <c r="L11" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N11" s="10" t="str">
         <f t="shared" si="4"/>
@@ -2691,22 +2700,22 @@
         <v>8：阿部悠真</v>
       </c>
     </row>
-    <row r="12" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F12" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E12,TankaData[コース],0)),0)</f>
@@ -2732,10 +2741,10 @@
         <v>37950</v>
       </c>
       <c r="L12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N12" s="10" t="str">
         <f t="shared" si="4"/>
@@ -2746,22 +2755,22 @@
         <v>9：石川凛</v>
       </c>
     </row>
-    <row r="13" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F13" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E13,TankaData[コース],0)),0)</f>
@@ -2787,10 +2796,10 @@
         <v>49500</v>
       </c>
       <c r="L13" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M13" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N13" s="10" t="str">
         <f t="shared" si="4"/>
@@ -2801,22 +2810,22 @@
         <v>10：木村美結</v>
       </c>
     </row>
-    <row r="14" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F14" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E14,TankaData[コース],0)),0)</f>
@@ -2842,10 +2851,10 @@
         <v>40260</v>
       </c>
       <c r="L14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N14" s="10" t="str">
         <f t="shared" si="4"/>
@@ -2856,22 +2865,22 @@
         <v>11：小林彩花</v>
       </c>
     </row>
-    <row r="15" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F15" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E15,TankaData[コース],0)),0)</f>
@@ -2897,10 +2906,10 @@
         <v>83600</v>
       </c>
       <c r="L15" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N15" s="10" t="str">
         <f t="shared" si="4"/>
@@ -2911,22 +2920,22 @@
         <v>12：吉田駿</v>
       </c>
     </row>
-    <row r="16" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F16" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E16,TankaData[コース],0)),0)</f>
@@ -2952,10 +2961,10 @@
         <v>22000</v>
       </c>
       <c r="L16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N16" s="10" t="str">
         <f t="shared" si="4"/>
@@ -2966,22 +2975,22 @@
         <v>13：竹内蓮</v>
       </c>
     </row>
-    <row r="17" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F17" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E17,TankaData[コース],0)),0)</f>
@@ -3007,10 +3016,10 @@
         <v>15950</v>
       </c>
       <c r="L17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="M17" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N17" s="10" t="str">
         <f t="shared" si="4"/>
@@ -3021,22 +3030,22 @@
         <v>14：木村優奈</v>
       </c>
     </row>
-    <row r="18" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F18" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E18,TankaData[コース],0)),0)</f>
@@ -3062,10 +3071,10 @@
         <v>26950</v>
       </c>
       <c r="L18" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="M18" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N18" s="10" t="str">
         <f t="shared" si="4"/>
@@ -3076,22 +3085,22 @@
         <v>15：村上悠斗</v>
       </c>
     </row>
-    <row r="19" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F19" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E19,TankaData[コース],0)),0)</f>
@@ -3117,10 +3126,10 @@
         <v>22000</v>
       </c>
       <c r="L19" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="M19" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N19" s="10" t="str">
         <f t="shared" si="4"/>
@@ -3131,22 +3140,22 @@
         <v>16：石川大翔</v>
       </c>
     </row>
-    <row r="20" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F20" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E20,TankaData[コース],0)),0)</f>
@@ -3172,10 +3181,10 @@
         <v>68200</v>
       </c>
       <c r="L20" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="M20" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N20" s="10" t="str">
         <f t="shared" si="4"/>
@@ -3186,22 +3195,22 @@
         <v>17：太田凛</v>
       </c>
     </row>
-    <row r="21" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F21" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E21,TankaData[コース],0)),0)</f>
@@ -3227,10 +3236,10 @@
         <v>40260</v>
       </c>
       <c r="L21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N21" s="10" t="str">
         <f t="shared" si="4"/>
@@ -3241,22 +3250,22 @@
         <v>18：吉田陽向</v>
       </c>
     </row>
-    <row r="22" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F22" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E22,TankaData[コース],0)),0)</f>
@@ -3282,10 +3291,10 @@
         <v>40260</v>
       </c>
       <c r="L22" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="M22" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N22" s="10" t="str">
         <f t="shared" si="4"/>
@@ -3296,22 +3305,22 @@
         <v>19：山下咲良</v>
       </c>
     </row>
-    <row r="23" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F23" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E23,TankaData[コース],0)),0)</f>
@@ -3337,10 +3346,10 @@
         <v>37400</v>
       </c>
       <c r="L23" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="M23" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N23" s="10" t="str">
         <f t="shared" si="4"/>
@@ -3351,22 +3360,22 @@
         <v>20：後藤愛</v>
       </c>
     </row>
-    <row r="24" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F24" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E24,TankaData[コース],0)),0)</f>
@@ -3392,10 +3401,10 @@
         <v>78100</v>
       </c>
       <c r="L24" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M24" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N24" s="10" t="str">
         <f t="shared" si="4"/>
@@ -3406,22 +3415,22 @@
         <v>21：田村美結</v>
       </c>
     </row>
-    <row r="25" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F25" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E25,TankaData[コース],0)),0)</f>
@@ -3447,10 +3456,10 @@
         <v>83600</v>
       </c>
       <c r="L25" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M25" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N25" s="10" t="str">
         <f t="shared" si="4"/>
@@ -3461,22 +3470,22 @@
         <v>22：中野陸</v>
       </c>
     </row>
-    <row r="26" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F26" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E26,TankaData[コース],0)),0)</f>
@@ -3502,10 +3511,10 @@
         <v>95700</v>
       </c>
       <c r="L26" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="M26" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N26" s="10" t="str">
         <f t="shared" si="4"/>
@@ -3516,22 +3525,22 @@
         <v>23：橋本颯</v>
       </c>
     </row>
-    <row r="27" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F27" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E27,TankaData[コース],0)),0)</f>
@@ -3557,10 +3566,10 @@
         <v>78100</v>
       </c>
       <c r="L27" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M27" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N27" s="10" t="str">
         <f t="shared" si="4"/>
@@ -3571,22 +3580,22 @@
         <v>24：林健太</v>
       </c>
     </row>
-    <row r="28" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F28" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E28,TankaData[コース],0)),0)</f>
@@ -3612,10 +3621,10 @@
         <v>49500</v>
       </c>
       <c r="L28" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="M28" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N28" s="10" t="str">
         <f t="shared" si="4"/>
@@ -3626,22 +3635,22 @@
         <v>25：金子美咲</v>
       </c>
     </row>
-    <row r="29" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F29" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E29,TankaData[コース],0)),0)</f>
@@ -3667,10 +3676,10 @@
         <v>48950</v>
       </c>
       <c r="L29" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="M29" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N29" s="10" t="str">
         <f t="shared" si="4"/>
@@ -3681,22 +3690,22 @@
         <v>26：山田結翔</v>
       </c>
     </row>
-    <row r="30" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F30" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E30,TankaData[コース],0)),0)</f>
@@ -3722,10 +3731,10 @@
         <v>49500</v>
       </c>
       <c r="L30" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="M30" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N30" s="10" t="str">
         <f t="shared" si="4"/>
@@ -3736,22 +3745,22 @@
         <v>27：田村拓也</v>
       </c>
     </row>
-    <row r="31" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F31" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E31,TankaData[コース],0)),0)</f>
@@ -3777,10 +3786,10 @@
         <v>68200</v>
       </c>
       <c r="L31" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M31" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N31" s="10" t="str">
         <f t="shared" si="4"/>
@@ -3791,22 +3800,22 @@
         <v>28：田中琴音</v>
       </c>
     </row>
-    <row r="32" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" s="5">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F32" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E32,TankaData[コース],0)),0)</f>
@@ -3832,10 +3841,10 @@
         <v>26950</v>
       </c>
       <c r="L32" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="M32" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N32" s="10" t="str">
         <f t="shared" si="4"/>
@@ -3846,22 +3855,22 @@
         <v>29：近藤悠斗</v>
       </c>
     </row>
-    <row r="33" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" s="5">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F33" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E33,TankaData[コース],0)),0)</f>
@@ -3887,10 +3896,10 @@
         <v>21780</v>
       </c>
       <c r="L33" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="M33" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N33" s="10" t="str">
         <f t="shared" si="4"/>
@@ -3901,22 +3910,22 @@
         <v>30：田中遥</v>
       </c>
     </row>
-    <row r="34" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" s="5">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F34" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E34,TankaData[コース],0)),0)</f>
@@ -3942,10 +3951,10 @@
         <v>12540</v>
       </c>
       <c r="L34" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="M34" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N34" s="10" t="str">
         <f t="shared" si="4"/>
@@ -3956,22 +3965,22 @@
         <v>31：森結衣</v>
       </c>
     </row>
-    <row r="35" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" s="5">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F35" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E35,TankaData[コース],0)),0)</f>
@@ -3997,10 +4006,10 @@
         <v>52800</v>
       </c>
       <c r="L35" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="M35" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N35" s="10" t="str">
         <f t="shared" si="4"/>
@@ -4011,22 +4020,22 @@
         <v>32：松本紬</v>
       </c>
     </row>
-    <row r="36" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" s="5">
         <f t="shared" ref="A36:A67" si="6">ROW()-3</f>
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F36" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E36,TankaData[コース],0)),0)</f>
@@ -4052,10 +4061,10 @@
         <v>59950</v>
       </c>
       <c r="L36" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="M36" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N36" s="10" t="str">
         <f t="shared" ref="N36:N67" si="10">"教室："&amp;C36&amp;"／コース："&amp;E36&amp;"／コマ数："&amp;H36&amp;"コマ／授業料："&amp;TEXT(J36,"#,##0")&amp;"円／教材費："&amp;TEXT(I36,"#,##0")&amp;"円／消費税："&amp;TEXT(ROUND((J36+I36)*0.1,0),"#,##0")&amp;"円／請求額："&amp;TEXT(K36,"#,##0")&amp;"円"</f>
@@ -4066,22 +4075,22 @@
         <v>33：後藤翼</v>
       </c>
     </row>
-    <row r="37" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" s="5">
         <f t="shared" si="6"/>
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F37" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E37,TankaData[コース],0)),0)</f>
@@ -4107,10 +4116,10 @@
         <v>37400</v>
       </c>
       <c r="L37" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M37" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N37" s="10" t="str">
         <f t="shared" si="10"/>
@@ -4121,22 +4130,22 @@
         <v>34：小野楓</v>
       </c>
     </row>
-    <row r="38" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" s="5">
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F38" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E38,TankaData[コース],0)),0)</f>
@@ -4162,10 +4171,10 @@
         <v>21780</v>
       </c>
       <c r="L38" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="M38" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N38" s="10" t="str">
         <f t="shared" si="10"/>
@@ -4176,22 +4185,22 @@
         <v>35：山下悠斗</v>
       </c>
     </row>
-    <row r="39" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" s="5">
         <f t="shared" si="6"/>
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F39" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E39,TankaData[コース],0)),0)</f>
@@ -4217,10 +4226,10 @@
         <v>78100</v>
       </c>
       <c r="L39" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="M39" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N39" s="10" t="str">
         <f t="shared" si="10"/>
@@ -4231,22 +4240,22 @@
         <v>36：藤田蓮</v>
       </c>
     </row>
-    <row r="40" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" s="5">
         <f t="shared" si="6"/>
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F40" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E40,TankaData[コース],0)),0)</f>
@@ -4272,10 +4281,10 @@
         <v>59950</v>
       </c>
       <c r="L40" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="M40" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N40" s="10" t="str">
         <f t="shared" si="10"/>
@@ -4286,22 +4295,22 @@
         <v>37：渡辺美結</v>
       </c>
     </row>
-    <row r="41" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" s="5">
         <f t="shared" si="6"/>
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F41" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E41,TankaData[コース],0)),0)</f>
@@ -4327,10 +4336,10 @@
         <v>12540</v>
       </c>
       <c r="L41" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="M41" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N41" s="10" t="str">
         <f t="shared" si="10"/>
@@ -4341,22 +4350,22 @@
         <v>38：斎藤葵</v>
       </c>
     </row>
-    <row r="42" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" s="5">
         <f t="shared" si="6"/>
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F42" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E42,TankaData[コース],0)),0)</f>
@@ -4382,10 +4391,10 @@
         <v>40260</v>
       </c>
       <c r="L42" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="M42" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N42" s="10" t="str">
         <f t="shared" si="10"/>
@@ -4396,22 +4405,22 @@
         <v>39：岡本蒼</v>
       </c>
     </row>
-    <row r="43" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" s="5">
         <f t="shared" si="6"/>
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F43" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E43,TankaData[コース],0)),0)</f>
@@ -4437,10 +4446,10 @@
         <v>40260</v>
       </c>
       <c r="L43" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="M43" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N43" s="10" t="str">
         <f t="shared" si="10"/>
@@ -4451,22 +4460,22 @@
         <v>40：小林美月</v>
       </c>
     </row>
-    <row r="44" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" s="5">
         <f t="shared" si="6"/>
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F44" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E44,TankaData[コース],0)),0)</f>
@@ -4492,10 +4501,10 @@
         <v>37950</v>
       </c>
       <c r="L44" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="M44" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N44" s="10" t="str">
         <f t="shared" si="10"/>
@@ -4506,22 +4515,22 @@
         <v>41：渡辺愛</v>
       </c>
     </row>
-    <row r="45" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" s="5">
         <f t="shared" si="6"/>
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F45" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E45,TankaData[コース],0)),0)</f>
@@ -4547,10 +4556,10 @@
         <v>49500</v>
       </c>
       <c r="L45" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="M45" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N45" s="10" t="str">
         <f t="shared" si="10"/>
@@ -4561,22 +4570,22 @@
         <v>42：高橋大翔</v>
       </c>
     </row>
-    <row r="46" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" s="5">
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F46" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E46,TankaData[コース],0)),0)</f>
@@ -4602,10 +4611,10 @@
         <v>68200</v>
       </c>
       <c r="L46" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="M46" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N46" s="10" t="str">
         <f t="shared" si="10"/>
@@ -4616,22 +4625,22 @@
         <v>43：田中詩織</v>
       </c>
     </row>
-    <row r="47" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" s="5">
         <f t="shared" si="6"/>
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F47" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E47,TankaData[コース],0)),0)</f>
@@ -4657,10 +4666,10 @@
         <v>48950</v>
       </c>
       <c r="L47" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="M47" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N47" s="10" t="str">
         <f t="shared" si="10"/>
@@ -4671,22 +4680,22 @@
         <v>44：井上美咲</v>
       </c>
     </row>
-    <row r="48" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" s="5">
         <f t="shared" si="6"/>
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F48" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E48,TankaData[コース],0)),0)</f>
@@ -4712,10 +4721,10 @@
         <v>78100</v>
       </c>
       <c r="L48" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="M48" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N48" s="10" t="str">
         <f t="shared" si="10"/>
@@ -4726,22 +4735,22 @@
         <v>45：渡辺葵</v>
       </c>
     </row>
-    <row r="49" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" s="5">
         <f t="shared" si="6"/>
         <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F49" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E49,TankaData[コース],0)),0)</f>
@@ -4767,10 +4776,10 @@
         <v>21780</v>
       </c>
       <c r="L49" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="M49" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N49" s="10" t="str">
         <f t="shared" si="10"/>
@@ -4781,22 +4790,22 @@
         <v>46：山崎詩織</v>
       </c>
     </row>
-    <row r="50" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" s="5">
         <f t="shared" si="6"/>
         <v>47</v>
       </c>
       <c r="B50" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F50" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E50,TankaData[コース],0)),0)</f>
@@ -4822,10 +4831,10 @@
         <v>83600</v>
       </c>
       <c r="L50" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M50" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N50" s="10" t="str">
         <f t="shared" si="10"/>
@@ -4836,22 +4845,22 @@
         <v>47：石井心春</v>
       </c>
     </row>
-    <row r="51" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" s="5">
         <f t="shared" si="6"/>
         <v>48</v>
       </c>
       <c r="B51" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F51" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E51,TankaData[コース],0)),0)</f>
@@ -4877,10 +4886,10 @@
         <v>78100</v>
       </c>
       <c r="L51" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="M51" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N51" s="10" t="str">
         <f t="shared" si="10"/>
@@ -4891,22 +4900,22 @@
         <v>48：佐藤健太</v>
       </c>
     </row>
-    <row r="52" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" s="5">
         <f t="shared" si="6"/>
         <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F52" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E52,TankaData[コース],0)),0)</f>
@@ -4932,10 +4941,10 @@
         <v>78100</v>
       </c>
       <c r="L52" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="M52" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N52" s="10" t="str">
         <f t="shared" si="10"/>
@@ -4946,22 +4955,22 @@
         <v>49：石井結衣</v>
       </c>
     </row>
-    <row r="53" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" s="5">
         <f t="shared" si="6"/>
         <v>50</v>
       </c>
       <c r="B53" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F53" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E53,TankaData[コース],0)),0)</f>
@@ -4987,10 +4996,10 @@
         <v>21780</v>
       </c>
       <c r="L53" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="M53" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N53" s="10" t="str">
         <f t="shared" si="10"/>
@@ -5001,22 +5010,22 @@
         <v>50：小川心春</v>
       </c>
     </row>
-    <row r="54" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" s="5">
         <f t="shared" si="6"/>
         <v>51</v>
       </c>
       <c r="B54" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F54" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E54,TankaData[コース],0)),0)</f>
@@ -5042,10 +5051,10 @@
         <v>48950</v>
       </c>
       <c r="L54" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="M54" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N54" s="10" t="str">
         <f t="shared" si="10"/>
@@ -5056,22 +5065,22 @@
         <v>51：青木彩花</v>
       </c>
     </row>
-    <row r="55" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" s="5">
         <f t="shared" si="6"/>
         <v>52</v>
       </c>
       <c r="B55" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F55" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E55,TankaData[コース],0)),0)</f>
@@ -5097,10 +5106,10 @@
         <v>68200</v>
       </c>
       <c r="L55" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="M55" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N55" s="10" t="str">
         <f t="shared" si="10"/>
@@ -5111,22 +5120,22 @@
         <v>52：福田蓮</v>
       </c>
     </row>
-    <row r="56" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" s="5">
         <f t="shared" si="6"/>
         <v>53</v>
       </c>
       <c r="B56" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F56" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E56,TankaData[コース],0)),0)</f>
@@ -5152,10 +5161,10 @@
         <v>48950</v>
       </c>
       <c r="L56" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M56" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N56" s="10" t="str">
         <f t="shared" si="10"/>
@@ -5166,22 +5175,22 @@
         <v>53：伊藤大輝</v>
       </c>
     </row>
-    <row r="57" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" s="5">
         <f t="shared" si="6"/>
         <v>54</v>
       </c>
       <c r="B57" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F57" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E57,TankaData[コース],0)),0)</f>
@@ -5207,10 +5216,10 @@
         <v>31020</v>
       </c>
       <c r="L57" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="M57" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N57" s="10" t="str">
         <f t="shared" si="10"/>
@@ -5221,22 +5230,22 @@
         <v>54：山下優奈</v>
       </c>
     </row>
-    <row r="58" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <f t="shared" si="6"/>
         <v>55</v>
       </c>
       <c r="B58" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F58" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E58,TankaData[コース],0)),0)</f>
@@ -5262,10 +5271,10 @@
         <v>12540</v>
       </c>
       <c r="L58" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="M58" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N58" s="10" t="str">
         <f t="shared" si="10"/>
@@ -5276,22 +5285,22 @@
         <v>55：橋本蓮</v>
       </c>
     </row>
-    <row r="59" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <f t="shared" si="6"/>
         <v>56</v>
       </c>
       <c r="B59" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F59" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E59,TankaData[コース],0)),0)</f>
@@ -5317,10 +5326,10 @@
         <v>60500</v>
       </c>
       <c r="L59" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="M59" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N59" s="10" t="str">
         <f t="shared" si="10"/>
@@ -5331,22 +5340,22 @@
         <v>56：遠藤彩花</v>
       </c>
     </row>
-    <row r="60" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <f t="shared" si="6"/>
         <v>57</v>
       </c>
       <c r="B60" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F60" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E60,TankaData[コース],0)),0)</f>
@@ -5372,10 +5381,10 @@
         <v>25300</v>
       </c>
       <c r="L60" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="M60" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N60" s="10" t="str">
         <f t="shared" si="10"/>
@@ -5386,22 +5395,22 @@
         <v>57：林一輝</v>
       </c>
     </row>
-    <row r="61" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <f t="shared" si="6"/>
         <v>58</v>
       </c>
       <c r="B61" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F61" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E61,TankaData[コース],0)),0)</f>
@@ -5427,10 +5436,10 @@
         <v>37400</v>
       </c>
       <c r="L61" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="M61" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N61" s="10" t="str">
         <f t="shared" si="10"/>
@@ -5441,22 +5450,22 @@
         <v>58：小野咲良</v>
       </c>
     </row>
-    <row r="62" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" s="5">
         <f t="shared" si="6"/>
         <v>59</v>
       </c>
       <c r="B62" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F62" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E62,TankaData[コース],0)),0)</f>
@@ -5482,10 +5491,10 @@
         <v>37400</v>
       </c>
       <c r="L62" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="M62" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N62" s="10" t="str">
         <f t="shared" si="10"/>
@@ -5496,22 +5505,22 @@
         <v>59：後藤紬</v>
       </c>
     </row>
-    <row r="63" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" s="5">
         <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="B63" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F63" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E63,TankaData[コース],0)),0)</f>
@@ -5537,10 +5546,10 @@
         <v>12540</v>
       </c>
       <c r="L63" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="M63" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N63" s="10" t="str">
         <f t="shared" si="10"/>
@@ -5551,22 +5560,22 @@
         <v>60：小林颯太</v>
       </c>
     </row>
-    <row r="64" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" s="5">
         <f t="shared" si="6"/>
         <v>61</v>
       </c>
       <c r="B64" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F64" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E64,TankaData[コース],0)),0)</f>
@@ -5592,10 +5601,10 @@
         <v>31020</v>
       </c>
       <c r="L64" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="M64" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N64" s="10" t="str">
         <f t="shared" si="10"/>
@@ -5606,22 +5615,22 @@
         <v>61：伊藤駿</v>
       </c>
     </row>
-    <row r="65" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" s="5">
         <f t="shared" si="6"/>
         <v>62</v>
       </c>
       <c r="B65" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F65" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E65,TankaData[コース],0)),0)</f>
@@ -5647,10 +5656,10 @@
         <v>83600</v>
       </c>
       <c r="L65" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M65" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N65" s="10" t="str">
         <f t="shared" si="10"/>
@@ -5661,22 +5670,22 @@
         <v>62：山下大和</v>
       </c>
     </row>
-    <row r="66" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" s="5">
         <f t="shared" si="6"/>
         <v>63</v>
       </c>
       <c r="B66" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F66" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E66,TankaData[コース],0)),0)</f>
@@ -5702,10 +5711,10 @@
         <v>52800</v>
       </c>
       <c r="L66" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="M66" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N66" s="10" t="str">
         <f t="shared" si="10"/>
@@ -5716,22 +5725,22 @@
         <v>63：後藤翔太</v>
       </c>
     </row>
-    <row r="67" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" s="5">
         <f t="shared" si="6"/>
         <v>64</v>
       </c>
       <c r="B67" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F67" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E67,TankaData[コース],0)),0)</f>
@@ -5757,10 +5766,10 @@
         <v>60500</v>
       </c>
       <c r="L67" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="M67" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N67" s="10" t="str">
         <f t="shared" si="10"/>
@@ -5771,22 +5780,22 @@
         <v>64：鈴木結衣</v>
       </c>
     </row>
-    <row r="68" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" s="5">
         <f t="shared" ref="A68:A99" si="12">ROW()-3</f>
         <v>65</v>
       </c>
       <c r="B68" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F68" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E68,TankaData[コース],0)),0)</f>
@@ -5812,10 +5821,10 @@
         <v>21780</v>
       </c>
       <c r="L68" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="M68" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N68" s="10" t="str">
         <f t="shared" ref="N68:N99" si="16">"教室："&amp;C68&amp;"／コース："&amp;E68&amp;"／コマ数："&amp;H68&amp;"コマ／授業料："&amp;TEXT(J68,"#,##0")&amp;"円／教材費："&amp;TEXT(I68,"#,##0")&amp;"円／消費税："&amp;TEXT(ROUND((J68+I68)*0.1,0),"#,##0")&amp;"円／請求額："&amp;TEXT(K68,"#,##0")&amp;"円"</f>
@@ -5826,22 +5835,22 @@
         <v>65：中野一輝</v>
       </c>
     </row>
-    <row r="69" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" s="5">
         <f t="shared" si="12"/>
         <v>66</v>
       </c>
       <c r="B69" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F69" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E69,TankaData[コース],0)),0)</f>
@@ -5867,10 +5876,10 @@
         <v>22000</v>
       </c>
       <c r="L69" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="M69" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N69" s="10" t="str">
         <f t="shared" si="16"/>
@@ -5881,22 +5890,22 @@
         <v>66：後藤湊</v>
       </c>
     </row>
-    <row r="70" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A70" s="5">
         <f t="shared" si="12"/>
         <v>67</v>
       </c>
       <c r="B70" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F70" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E70,TankaData[コース],0)),0)</f>
@@ -5922,10 +5931,10 @@
         <v>95700</v>
       </c>
       <c r="L70" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="M70" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N70" s="10" t="str">
         <f t="shared" si="16"/>
@@ -5936,22 +5945,22 @@
         <v>67：佐々木さくら</v>
       </c>
     </row>
-    <row r="71" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A71" s="5">
         <f t="shared" si="12"/>
         <v>68</v>
       </c>
       <c r="B71" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F71" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E71,TankaData[コース],0)),0)</f>
@@ -5977,10 +5986,10 @@
         <v>59950</v>
       </c>
       <c r="L71" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="M71" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N71" s="10" t="str">
         <f t="shared" si="16"/>
@@ -5991,22 +6000,22 @@
         <v>68：松本拓也</v>
       </c>
     </row>
-    <row r="72" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" s="5">
         <f t="shared" si="12"/>
         <v>69</v>
       </c>
       <c r="B72" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F72" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E72,TankaData[コース],0)),0)</f>
@@ -6032,10 +6041,10 @@
         <v>15950</v>
       </c>
       <c r="L72" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="M72" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N72" s="10" t="str">
         <f t="shared" si="16"/>
@@ -6046,22 +6055,22 @@
         <v>69：高橋陽菜</v>
       </c>
     </row>
-    <row r="73" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" s="5">
         <f t="shared" si="12"/>
         <v>70</v>
       </c>
       <c r="B73" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F73" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E73,TankaData[コース],0)),0)</f>
@@ -6087,10 +6096,10 @@
         <v>15950</v>
       </c>
       <c r="L73" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="M73" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N73" s="10" t="str">
         <f t="shared" si="16"/>
@@ -6101,22 +6110,22 @@
         <v>70：青木湊</v>
       </c>
     </row>
-    <row r="74" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" s="5">
         <f t="shared" si="12"/>
         <v>71</v>
       </c>
       <c r="B74" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F74" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E74,TankaData[コース],0)),0)</f>
@@ -6142,10 +6151,10 @@
         <v>12540</v>
       </c>
       <c r="L74" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="M74" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N74" s="10" t="str">
         <f t="shared" si="16"/>
@@ -6156,22 +6165,22 @@
         <v>71：鈴木琴音</v>
       </c>
     </row>
-    <row r="75" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A75" s="5">
         <f t="shared" si="12"/>
         <v>72</v>
       </c>
       <c r="B75" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F75" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E75,TankaData[コース],0)),0)</f>
@@ -6197,10 +6206,10 @@
         <v>48950</v>
       </c>
       <c r="L75" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="M75" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N75" s="10" t="str">
         <f t="shared" si="16"/>
@@ -6211,22 +6220,22 @@
         <v>72：岡本彩花</v>
       </c>
     </row>
-    <row r="76" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" s="5">
         <f t="shared" si="12"/>
         <v>73</v>
       </c>
       <c r="B76" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F76" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E76,TankaData[コース],0)),0)</f>
@@ -6252,10 +6261,10 @@
         <v>21780</v>
       </c>
       <c r="L76" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="M76" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N76" s="10" t="str">
         <f t="shared" si="16"/>
@@ -6266,22 +6275,22 @@
         <v>73：井上蓮</v>
       </c>
     </row>
-    <row r="77" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" s="5">
         <f t="shared" si="12"/>
         <v>74</v>
       </c>
       <c r="B77" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F77" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E77,TankaData[コース],0)),0)</f>
@@ -6307,10 +6316,10 @@
         <v>59950</v>
       </c>
       <c r="L77" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="M77" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N77" s="10" t="str">
         <f t="shared" si="16"/>
@@ -6321,22 +6330,22 @@
         <v>74：加藤一輝</v>
       </c>
     </row>
-    <row r="78" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" s="5">
         <f t="shared" si="12"/>
         <v>75</v>
       </c>
       <c r="B78" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F78" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E78,TankaData[コース],0)),0)</f>
@@ -6362,10 +6371,10 @@
         <v>40260</v>
       </c>
       <c r="L78" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="M78" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N78" s="10" t="str">
         <f t="shared" si="16"/>
@@ -6376,22 +6385,22 @@
         <v>75：渡辺煌</v>
       </c>
     </row>
-    <row r="79" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A79" s="5">
         <f t="shared" si="12"/>
         <v>76</v>
       </c>
       <c r="B79" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F79" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E79,TankaData[コース],0)),0)</f>
@@ -6417,10 +6426,10 @@
         <v>37950</v>
       </c>
       <c r="L79" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="M79" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N79" s="10" t="str">
         <f t="shared" si="16"/>
@@ -6431,22 +6440,22 @@
         <v>76：小川美月</v>
       </c>
     </row>
-    <row r="80" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" s="5">
         <f t="shared" si="12"/>
         <v>77</v>
       </c>
       <c r="B80" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F80" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E80,TankaData[コース],0)),0)</f>
@@ -6472,10 +6481,10 @@
         <v>60500</v>
       </c>
       <c r="L80" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="M80" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N80" s="10" t="str">
         <f t="shared" si="16"/>
@@ -6486,22 +6495,22 @@
         <v>77：岡本陽向</v>
       </c>
     </row>
-    <row r="81" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A81" s="5">
         <f t="shared" si="12"/>
         <v>78</v>
       </c>
       <c r="B81" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F81" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E81,TankaData[コース],0)),0)</f>
@@ -6527,10 +6536,10 @@
         <v>68200</v>
       </c>
       <c r="L81" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M81" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N81" s="10" t="str">
         <f t="shared" si="16"/>
@@ -6541,22 +6550,22 @@
         <v>78：小川陽向</v>
       </c>
     </row>
-    <row r="82" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A82" s="5">
         <f t="shared" si="12"/>
         <v>79</v>
       </c>
       <c r="B82" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F82" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E82,TankaData[コース],0)),0)</f>
@@ -6582,10 +6591,10 @@
         <v>15950</v>
       </c>
       <c r="L82" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="M82" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N82" s="10" t="str">
         <f t="shared" si="16"/>
@@ -6596,22 +6605,22 @@
         <v>79：田中結衣</v>
       </c>
     </row>
-    <row r="83" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A83" s="5">
         <f t="shared" si="12"/>
         <v>80</v>
       </c>
       <c r="B83" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F83" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E83,TankaData[コース],0)),0)</f>
@@ -6637,10 +6646,10 @@
         <v>26950</v>
       </c>
       <c r="L83" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="M83" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N83" s="10" t="str">
         <f t="shared" si="16"/>
@@ -6651,22 +6660,22 @@
         <v>80：橋本煌</v>
       </c>
     </row>
-    <row r="84" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A84" s="5">
         <f t="shared" si="12"/>
         <v>81</v>
       </c>
       <c r="B84" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F84" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E84,TankaData[コース],0)),0)</f>
@@ -6692,10 +6701,10 @@
         <v>52800</v>
       </c>
       <c r="L84" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="M84" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N84" s="10" t="str">
         <f t="shared" si="16"/>
@@ -6706,22 +6715,22 @@
         <v>81：松本萌</v>
       </c>
     </row>
-    <row r="85" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A85" s="5">
         <f t="shared" si="12"/>
         <v>82</v>
       </c>
       <c r="B85" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F85" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E85,TankaData[コース],0)),0)</f>
@@ -6747,10 +6756,10 @@
         <v>37950</v>
       </c>
       <c r="L85" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="M85" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N85" s="10" t="str">
         <f t="shared" si="16"/>
@@ -6761,22 +6770,22 @@
         <v>82：小野結衣</v>
       </c>
     </row>
-    <row r="86" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A86" s="5">
         <f t="shared" si="12"/>
         <v>83</v>
       </c>
       <c r="B86" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F86" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E86,TankaData[コース],0)),0)</f>
@@ -6802,10 +6811,10 @@
         <v>95700</v>
       </c>
       <c r="L86" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="M86" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N86" s="10" t="str">
         <f t="shared" si="16"/>
@@ -6816,22 +6825,22 @@
         <v>83：藤井陽向</v>
       </c>
     </row>
-    <row r="87" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A87" s="5">
         <f t="shared" si="12"/>
         <v>84</v>
       </c>
       <c r="B87" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F87" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E87,TankaData[コース],0)),0)</f>
@@ -6857,10 +6866,10 @@
         <v>42900</v>
       </c>
       <c r="L87" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="M87" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N87" s="10" t="str">
         <f t="shared" si="16"/>
@@ -6871,22 +6880,22 @@
         <v>84：村上尊</v>
       </c>
     </row>
-    <row r="88" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A88" s="5">
         <f t="shared" si="12"/>
         <v>85</v>
       </c>
       <c r="B88" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F88" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E88,TankaData[コース],0)),0)</f>
@@ -6912,10 +6921,10 @@
         <v>49500</v>
       </c>
       <c r="L88" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="M88" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N88" s="10" t="str">
         <f t="shared" si="16"/>
@@ -6926,22 +6935,22 @@
         <v>85：山田花音</v>
       </c>
     </row>
-    <row r="89" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A89" s="5">
         <f t="shared" si="12"/>
         <v>86</v>
       </c>
       <c r="B89" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F89" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E89,TankaData[コース],0)),0)</f>
@@ -6967,10 +6976,10 @@
         <v>40260</v>
       </c>
       <c r="L89" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="M89" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N89" s="10" t="str">
         <f t="shared" si="16"/>
@@ -6981,22 +6990,22 @@
         <v>86：小川駿</v>
       </c>
     </row>
-    <row r="90" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A90" s="5">
         <f t="shared" si="12"/>
         <v>87</v>
       </c>
       <c r="B90" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F90" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E90,TankaData[コース],0)),0)</f>
@@ -7022,10 +7031,10 @@
         <v>25300</v>
       </c>
       <c r="L90" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="M90" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N90" s="10" t="str">
         <f t="shared" si="16"/>
@@ -7036,22 +7045,22 @@
         <v>87：中野健太</v>
       </c>
     </row>
-    <row r="91" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A91" s="5">
         <f t="shared" si="12"/>
         <v>88</v>
       </c>
       <c r="B91" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F91" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E91,TankaData[コース],0)),0)</f>
@@ -7077,10 +7086,10 @@
         <v>68200</v>
       </c>
       <c r="L91" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M91" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N91" s="10" t="str">
         <f t="shared" si="16"/>
@@ -7091,22 +7100,22 @@
         <v>88：田中結翔</v>
       </c>
     </row>
-    <row r="92" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A92" s="5">
         <f t="shared" si="12"/>
         <v>89</v>
       </c>
       <c r="B92" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F92" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E92,TankaData[コース],0)),0)</f>
@@ -7132,10 +7141,10 @@
         <v>59950</v>
       </c>
       <c r="L92" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="M92" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N92" s="10" t="str">
         <f t="shared" si="16"/>
@@ -7146,22 +7155,22 @@
         <v>89：伊藤翼</v>
       </c>
     </row>
-    <row r="93" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A93" s="5">
         <f t="shared" si="12"/>
         <v>90</v>
       </c>
       <c r="B93" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F93" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E93,TankaData[コース],0)),0)</f>
@@ -7187,10 +7196,10 @@
         <v>49500</v>
       </c>
       <c r="L93" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M93" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N93" s="10" t="str">
         <f t="shared" si="16"/>
@@ -7201,22 +7210,22 @@
         <v>90：後藤颯太</v>
       </c>
     </row>
-    <row r="94" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A94" s="5">
         <f t="shared" si="12"/>
         <v>91</v>
       </c>
       <c r="B94" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F94" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E94,TankaData[コース],0)),0)</f>
@@ -7242,10 +7251,10 @@
         <v>48950</v>
       </c>
       <c r="L94" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="M94" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N94" s="10" t="str">
         <f t="shared" si="16"/>
@@ -7256,22 +7265,22 @@
         <v>91：井上大和</v>
       </c>
     </row>
-    <row r="95" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A95" s="5">
         <f t="shared" si="12"/>
         <v>92</v>
       </c>
       <c r="B95" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F95" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E95,TankaData[コース],0)),0)</f>
@@ -7297,10 +7306,10 @@
         <v>37950</v>
       </c>
       <c r="L95" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="M95" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N95" s="10" t="str">
         <f t="shared" si="16"/>
@@ -7311,22 +7320,22 @@
         <v>92：井上詩織</v>
       </c>
     </row>
-    <row r="96" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A96" s="5">
         <f t="shared" si="12"/>
         <v>93</v>
       </c>
       <c r="B96" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F96" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E96,TankaData[コース],0)),0)</f>
@@ -7352,10 +7361,10 @@
         <v>37950</v>
       </c>
       <c r="L96" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="M96" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N96" s="10" t="str">
         <f t="shared" si="16"/>
@@ -7366,22 +7375,22 @@
         <v>93：中島琴音</v>
       </c>
     </row>
-    <row r="97" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A97" s="5">
         <f t="shared" si="12"/>
         <v>94</v>
       </c>
       <c r="B97" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F97" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E97,TankaData[コース],0)),0)</f>
@@ -7407,10 +7416,10 @@
         <v>22000</v>
       </c>
       <c r="L97" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="M97" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N97" s="10" t="str">
         <f t="shared" si="16"/>
@@ -7421,22 +7430,22 @@
         <v>94：山本拓也</v>
       </c>
     </row>
-    <row r="98" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A98" s="5">
         <f t="shared" si="12"/>
         <v>95</v>
       </c>
       <c r="B98" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F98" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E98,TankaData[コース],0)),0)</f>
@@ -7462,10 +7471,10 @@
         <v>15950</v>
       </c>
       <c r="L98" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="M98" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N98" s="10" t="str">
         <f t="shared" si="16"/>
@@ -7476,22 +7485,22 @@
         <v>95：池田颯</v>
       </c>
     </row>
-    <row r="99" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A99" s="5">
         <f t="shared" si="12"/>
         <v>96</v>
       </c>
       <c r="B99" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F99" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E99,TankaData[コース],0)),0)</f>
@@ -7517,10 +7526,10 @@
         <v>37400</v>
       </c>
       <c r="L99" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="M99" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N99" s="10" t="str">
         <f t="shared" si="16"/>
@@ -7531,22 +7540,22 @@
         <v>96：斎藤彩花</v>
       </c>
     </row>
-    <row r="100" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A100" s="5">
         <f t="shared" ref="A100:A131" si="18">ROW()-3</f>
         <v>97</v>
       </c>
       <c r="B100" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F100" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E100,TankaData[コース],0)),0)</f>
@@ -7572,10 +7581,10 @@
         <v>31020</v>
       </c>
       <c r="L100" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="M100" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N100" s="10" t="str">
         <f t="shared" ref="N100:N131" si="22">"教室："&amp;C100&amp;"／コース："&amp;E100&amp;"／コマ数："&amp;H100&amp;"コマ／授業料："&amp;TEXT(J100,"#,##0")&amp;"円／教材費："&amp;TEXT(I100,"#,##0")&amp;"円／消費税："&amp;TEXT(ROUND((J100+I100)*0.1,0),"#,##0")&amp;"円／請求額："&amp;TEXT(K100,"#,##0")&amp;"円"</f>
@@ -7586,22 +7595,22 @@
         <v>97：山本愛</v>
       </c>
     </row>
-    <row r="101" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A101" s="5">
         <f t="shared" si="18"/>
         <v>98</v>
       </c>
       <c r="B101" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F101" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E101,TankaData[コース],0)),0)</f>
@@ -7627,10 +7636,10 @@
         <v>15950</v>
       </c>
       <c r="L101" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M101" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N101" s="10" t="str">
         <f t="shared" si="22"/>
@@ -7641,22 +7650,22 @@
         <v>98：小野美咲</v>
       </c>
     </row>
-    <row r="102" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A102" s="5">
         <f t="shared" si="18"/>
         <v>99</v>
       </c>
       <c r="B102" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F102" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E102,TankaData[コース],0)),0)</f>
@@ -7682,10 +7691,10 @@
         <v>26950</v>
       </c>
       <c r="L102" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="M102" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N102" s="10" t="str">
         <f t="shared" si="22"/>
@@ -7696,22 +7705,22 @@
         <v>99：石川美咲</v>
       </c>
     </row>
-    <row r="103" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A103" s="5">
         <f t="shared" si="18"/>
         <v>100</v>
       </c>
       <c r="B103" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F103" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E103,TankaData[コース],0)),0)</f>
@@ -7737,10 +7746,10 @@
         <v>52800</v>
       </c>
       <c r="L103" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="M103" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N103" s="10" t="str">
         <f t="shared" si="22"/>
@@ -7751,22 +7760,22 @@
         <v>100：阿部拓也</v>
       </c>
     </row>
-    <row r="104" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A104" s="5">
         <f t="shared" si="18"/>
         <v>101</v>
       </c>
       <c r="B104" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F104" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E104,TankaData[コース],0)),0)</f>
@@ -7792,10 +7801,10 @@
         <v>52800</v>
       </c>
       <c r="L104" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M104" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N104" s="10" t="str">
         <f t="shared" si="22"/>
@@ -7806,22 +7815,22 @@
         <v>101：西村彩花</v>
       </c>
     </row>
-    <row r="105" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A105" s="5">
         <f t="shared" si="18"/>
         <v>102</v>
       </c>
       <c r="B105" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F105" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E105,TankaData[コース],0)),0)</f>
@@ -7847,10 +7856,10 @@
         <v>95700</v>
       </c>
       <c r="L105" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="M105" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N105" s="10" t="str">
         <f t="shared" si="22"/>
@@ -7861,22 +7870,22 @@
         <v>102：森健太</v>
       </c>
     </row>
-    <row r="106" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A106" s="5">
         <f t="shared" si="18"/>
         <v>103</v>
       </c>
       <c r="B106" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F106" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E106,TankaData[コース],0)),0)</f>
@@ -7902,10 +7911,10 @@
         <v>68200</v>
       </c>
       <c r="L106" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="M106" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N106" s="10" t="str">
         <f t="shared" si="22"/>
@@ -7916,22 +7925,22 @@
         <v>103：伊藤悠真</v>
       </c>
     </row>
-    <row r="107" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A107" s="5">
         <f t="shared" si="18"/>
         <v>104</v>
       </c>
       <c r="B107" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F107" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E107,TankaData[コース],0)),0)</f>
@@ -7957,10 +7966,10 @@
         <v>95700</v>
       </c>
       <c r="L107" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="M107" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N107" s="10" t="str">
         <f t="shared" si="22"/>
@@ -7971,22 +7980,22 @@
         <v>104：松本大輝</v>
       </c>
     </row>
-    <row r="108" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A108" s="5">
         <f t="shared" si="18"/>
         <v>105</v>
       </c>
       <c r="B108" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F108" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E108,TankaData[コース],0)),0)</f>
@@ -8012,10 +8021,10 @@
         <v>40260</v>
       </c>
       <c r="L108" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="M108" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N108" s="10" t="str">
         <f t="shared" si="22"/>
@@ -8026,22 +8035,22 @@
         <v>105：太田拓也</v>
       </c>
     </row>
-    <row r="109" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A109" s="5">
         <f t="shared" si="18"/>
         <v>106</v>
       </c>
       <c r="B109" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F109" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E109,TankaData[コース],0)),0)</f>
@@ -8067,10 +8076,10 @@
         <v>26950</v>
       </c>
       <c r="L109" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="M109" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N109" s="10" t="str">
         <f t="shared" si="22"/>
@@ -8081,22 +8090,22 @@
         <v>106：中島悠真</v>
       </c>
     </row>
-    <row r="110" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A110" s="5">
         <f t="shared" si="18"/>
         <v>107</v>
       </c>
       <c r="B110" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F110" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E110,TankaData[コース],0)),0)</f>
@@ -8122,10 +8131,10 @@
         <v>48950</v>
       </c>
       <c r="L110" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M110" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N110" s="10" t="str">
         <f t="shared" si="22"/>
@@ -8136,22 +8145,22 @@
         <v>107：中野咲良</v>
       </c>
     </row>
-    <row r="111" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A111" s="5">
         <f t="shared" si="18"/>
         <v>108</v>
       </c>
       <c r="B111" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F111" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E111,TankaData[コース],0)),0)</f>
@@ -8177,10 +8186,10 @@
         <v>78100</v>
       </c>
       <c r="L111" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="M111" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N111" s="10" t="str">
         <f t="shared" si="22"/>
@@ -8191,22 +8200,22 @@
         <v>108：吉田優奈</v>
       </c>
     </row>
-    <row r="112" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A112" s="5">
         <f t="shared" si="18"/>
         <v>109</v>
       </c>
       <c r="B112" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F112" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E112,TankaData[コース],0)),0)</f>
@@ -8232,10 +8241,10 @@
         <v>95700</v>
       </c>
       <c r="L112" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="M112" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N112" s="10" t="str">
         <f t="shared" si="22"/>
@@ -8246,22 +8255,22 @@
         <v>109：林大翔</v>
       </c>
     </row>
-    <row r="113" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A113" s="5">
         <f t="shared" si="18"/>
         <v>110</v>
       </c>
       <c r="B113" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F113" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E113,TankaData[コース],0)),0)</f>
@@ -8287,10 +8296,10 @@
         <v>37400</v>
       </c>
       <c r="L113" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="M113" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N113" s="10" t="str">
         <f t="shared" si="22"/>
@@ -8301,22 +8310,22 @@
         <v>110：青木陽菜</v>
       </c>
     </row>
-    <row r="114" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A114" s="5">
         <f t="shared" si="18"/>
         <v>111</v>
       </c>
       <c r="B114" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F114" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E114,TankaData[コース],0)),0)</f>
@@ -8342,10 +8351,10 @@
         <v>42900</v>
       </c>
       <c r="L114" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="M114" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N114" s="10" t="str">
         <f t="shared" si="22"/>
@@ -8356,22 +8365,22 @@
         <v>111：清水一輝</v>
       </c>
     </row>
-    <row r="115" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A115" s="5">
         <f t="shared" si="18"/>
         <v>112</v>
       </c>
       <c r="B115" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F115" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E115,TankaData[コース],0)),0)</f>
@@ -8397,10 +8406,10 @@
         <v>49500</v>
       </c>
       <c r="L115" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="M115" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N115" s="10" t="str">
         <f t="shared" si="22"/>
@@ -8411,22 +8420,22 @@
         <v>112：井上朝陽</v>
       </c>
     </row>
-    <row r="116" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A116" s="5">
         <f t="shared" si="18"/>
         <v>113</v>
       </c>
       <c r="B116" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F116" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E116,TankaData[コース],0)),0)</f>
@@ -8452,10 +8461,10 @@
         <v>40260</v>
       </c>
       <c r="L116" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="M116" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N116" s="10" t="str">
         <f t="shared" si="22"/>
@@ -8466,22 +8475,22 @@
         <v>113：中野美桜</v>
       </c>
     </row>
-    <row r="117" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A117" s="5">
         <f t="shared" si="18"/>
         <v>114</v>
       </c>
       <c r="B117" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F117" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E117,TankaData[コース],0)),0)</f>
@@ -8507,10 +8516,10 @@
         <v>59950</v>
       </c>
       <c r="L117" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="M117" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N117" s="10" t="str">
         <f t="shared" si="22"/>
@@ -8521,22 +8530,22 @@
         <v>114：林美月</v>
       </c>
     </row>
-    <row r="118" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A118" s="5">
         <f t="shared" si="18"/>
         <v>115</v>
       </c>
       <c r="B118" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F118" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E118,TankaData[コース],0)),0)</f>
@@ -8562,10 +8571,10 @@
         <v>59950</v>
       </c>
       <c r="L118" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="M118" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N118" s="10" t="str">
         <f t="shared" si="22"/>
@@ -8576,22 +8585,22 @@
         <v>115：加藤悠斗</v>
       </c>
     </row>
-    <row r="119" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A119" s="5">
         <f t="shared" si="18"/>
         <v>116</v>
       </c>
       <c r="B119" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F119" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E119,TankaData[コース],0)),0)</f>
@@ -8617,10 +8626,10 @@
         <v>42900</v>
       </c>
       <c r="L119" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="M119" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N119" s="10" t="str">
         <f t="shared" si="22"/>
@@ -8631,22 +8640,22 @@
         <v>116：福田結衣</v>
       </c>
     </row>
-    <row r="120" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A120" s="5">
         <f t="shared" si="18"/>
         <v>117</v>
       </c>
       <c r="B120" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F120" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E120,TankaData[コース],0)),0)</f>
@@ -8672,10 +8681,10 @@
         <v>15950</v>
       </c>
       <c r="L120" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="M120" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N120" s="10" t="str">
         <f t="shared" si="22"/>
@@ -8686,22 +8695,22 @@
         <v>117：山口陽向</v>
       </c>
     </row>
-    <row r="121" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A121" s="5">
         <f t="shared" si="18"/>
         <v>118</v>
       </c>
       <c r="B121" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F121" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E121,TankaData[コース],0)),0)</f>
@@ -8727,10 +8736,10 @@
         <v>37400</v>
       </c>
       <c r="L121" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M121" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N121" s="10" t="str">
         <f t="shared" si="22"/>
@@ -8741,22 +8750,22 @@
         <v>118：高橋蒼</v>
       </c>
     </row>
-    <row r="122" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A122" s="5">
         <f t="shared" si="18"/>
         <v>119</v>
       </c>
       <c r="B122" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F122" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E122,TankaData[コース],0)),0)</f>
@@ -8782,10 +8791,10 @@
         <v>42900</v>
       </c>
       <c r="L122" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="M122" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N122" s="10" t="str">
         <f t="shared" si="22"/>
@@ -8796,22 +8805,22 @@
         <v>119：林翔太</v>
       </c>
     </row>
-    <row r="123" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A123" s="5">
         <f t="shared" si="18"/>
         <v>120</v>
       </c>
       <c r="B123" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F123" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E123,TankaData[コース],0)),0)</f>
@@ -8837,10 +8846,10 @@
         <v>40260</v>
       </c>
       <c r="L123" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="M123" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N123" s="10" t="str">
         <f t="shared" si="22"/>
@@ -8851,22 +8860,22 @@
         <v>120：岡田詩織</v>
       </c>
     </row>
-    <row r="124" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A124" s="5">
         <f t="shared" si="18"/>
         <v>121</v>
       </c>
       <c r="B124" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F124" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E124,TankaData[コース],0)),0)</f>
@@ -8892,10 +8901,10 @@
         <v>15950</v>
       </c>
       <c r="L124" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="M124" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N124" s="10" t="str">
         <f t="shared" si="22"/>
@@ -8906,22 +8915,22 @@
         <v>121：後藤蒼</v>
       </c>
     </row>
-    <row r="125" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A125" s="5">
         <f t="shared" si="18"/>
         <v>122</v>
       </c>
       <c r="B125" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F125" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E125,TankaData[コース],0)),0)</f>
@@ -8947,10 +8956,10 @@
         <v>37950</v>
       </c>
       <c r="L125" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="M125" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N125" s="10" t="str">
         <f t="shared" si="22"/>
@@ -8961,22 +8970,22 @@
         <v>122：渡辺陽菜乃</v>
       </c>
     </row>
-    <row r="126" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A126" s="5">
         <f t="shared" si="18"/>
         <v>123</v>
       </c>
       <c r="B126" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F126" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E126,TankaData[コース],0)),0)</f>
@@ -9002,10 +9011,10 @@
         <v>42900</v>
       </c>
       <c r="L126" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="M126" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N126" s="10" t="str">
         <f t="shared" si="22"/>
@@ -9016,22 +9025,22 @@
         <v>123：小川一輝</v>
       </c>
     </row>
-    <row r="127" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A127" s="5">
         <f t="shared" si="18"/>
         <v>124</v>
       </c>
       <c r="B127" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F127" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E127,TankaData[コース],0)),0)</f>
@@ -9057,10 +9066,10 @@
         <v>68200</v>
       </c>
       <c r="L127" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="M127" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N127" s="10" t="str">
         <f t="shared" si="22"/>
@@ -9071,22 +9080,22 @@
         <v>124：斎藤愛</v>
       </c>
     </row>
-    <row r="128" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A128" s="5">
         <f t="shared" si="18"/>
         <v>125</v>
       </c>
       <c r="B128" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F128" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E128,TankaData[コース],0)),0)</f>
@@ -9112,10 +9121,10 @@
         <v>37400</v>
       </c>
       <c r="L128" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="M128" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N128" s="10" t="str">
         <f t="shared" si="22"/>
@@ -9126,22 +9135,22 @@
         <v>125：長谷川咲良</v>
       </c>
     </row>
-    <row r="129" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A129" s="5">
         <f t="shared" si="18"/>
         <v>126</v>
       </c>
       <c r="B129" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F129" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E129,TankaData[コース],0)),0)</f>
@@ -9167,10 +9176,10 @@
         <v>22000</v>
       </c>
       <c r="L129" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="M129" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N129" s="10" t="str">
         <f t="shared" si="22"/>
@@ -9181,22 +9190,22 @@
         <v>126：長谷川煌</v>
       </c>
     </row>
-    <row r="130" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A130" s="5">
         <f t="shared" si="18"/>
         <v>127</v>
       </c>
       <c r="B130" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F130" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E130,TankaData[コース],0)),0)</f>
@@ -9222,10 +9231,10 @@
         <v>52800</v>
       </c>
       <c r="L130" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="M130" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N130" s="10" t="str">
         <f t="shared" si="22"/>
@@ -9236,22 +9245,22 @@
         <v>127：吉田萌</v>
       </c>
     </row>
-    <row r="131" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A131" s="5">
         <f t="shared" si="18"/>
         <v>128</v>
       </c>
       <c r="B131" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F131" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E131,TankaData[コース],0)),0)</f>
@@ -9277,10 +9286,10 @@
         <v>12540</v>
       </c>
       <c r="L131" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M131" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N131" s="10" t="str">
         <f t="shared" si="22"/>
@@ -9291,22 +9300,22 @@
         <v>128：山本一輝</v>
       </c>
     </row>
-    <row r="132" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A132" s="5">
         <f t="shared" ref="A132:A163" si="24">ROW()-3</f>
         <v>129</v>
       </c>
       <c r="B132" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F132" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E132,TankaData[コース],0)),0)</f>
@@ -9332,10 +9341,10 @@
         <v>48950</v>
       </c>
       <c r="L132" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="M132" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N132" s="10" t="str">
         <f t="shared" ref="N132:N163" si="28">"教室："&amp;C132&amp;"／コース："&amp;E132&amp;"／コマ数："&amp;H132&amp;"コマ／授業料："&amp;TEXT(J132,"#,##0")&amp;"円／教材費："&amp;TEXT(I132,"#,##0")&amp;"円／消費税："&amp;TEXT(ROUND((J132+I132)*0.1,0),"#,##0")&amp;"円／請求額："&amp;TEXT(K132,"#,##0")&amp;"円"</f>
@@ -9346,22 +9355,22 @@
         <v>129：坂本凛</v>
       </c>
     </row>
-    <row r="133" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A133" s="5">
         <f t="shared" si="24"/>
         <v>130</v>
       </c>
       <c r="B133" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F133" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E133,TankaData[コース],0)),0)</f>
@@ -9387,10 +9396,10 @@
         <v>40260</v>
       </c>
       <c r="L133" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="M133" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N133" s="10" t="str">
         <f t="shared" si="28"/>
@@ -9401,22 +9410,22 @@
         <v>130：佐藤蒼</v>
       </c>
     </row>
-    <row r="134" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A134" s="5">
         <f t="shared" si="24"/>
         <v>131</v>
       </c>
       <c r="B134" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F134" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E134,TankaData[コース],0)),0)</f>
@@ -9442,10 +9451,10 @@
         <v>78100</v>
       </c>
       <c r="L134" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="M134" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N134" s="10" t="str">
         <f t="shared" si="28"/>
@@ -9456,22 +9465,22 @@
         <v>131：前田結翔</v>
       </c>
     </row>
-    <row r="135" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A135" s="5">
         <f t="shared" si="24"/>
         <v>132</v>
       </c>
       <c r="B135" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F135" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E135,TankaData[コース],0)),0)</f>
@@ -9497,10 +9506,10 @@
         <v>15950</v>
       </c>
       <c r="L135" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="M135" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N135" s="10" t="str">
         <f t="shared" si="28"/>
@@ -9511,22 +9520,22 @@
         <v>132：竹内蒼</v>
       </c>
     </row>
-    <row r="136" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A136" s="5">
         <f t="shared" si="24"/>
         <v>133</v>
       </c>
       <c r="B136" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F136" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E136,TankaData[コース],0)),0)</f>
@@ -9552,10 +9561,10 @@
         <v>83600</v>
       </c>
       <c r="L136" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="M136" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N136" s="10" t="str">
         <f t="shared" si="28"/>
@@ -9566,22 +9575,22 @@
         <v>133：加藤葵</v>
       </c>
     </row>
-    <row r="137" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A137" s="5">
         <f t="shared" si="24"/>
         <v>134</v>
       </c>
       <c r="B137" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F137" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E137,TankaData[コース],0)),0)</f>
@@ -9607,10 +9616,10 @@
         <v>59950</v>
       </c>
       <c r="L137" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M137" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N137" s="10" t="str">
         <f t="shared" si="28"/>
@@ -9621,22 +9630,22 @@
         <v>134：佐藤萌</v>
       </c>
     </row>
-    <row r="138" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A138" s="5">
         <f t="shared" si="24"/>
         <v>135</v>
       </c>
       <c r="B138" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F138" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E138,TankaData[コース],0)),0)</f>
@@ -9662,10 +9671,10 @@
         <v>68200</v>
       </c>
       <c r="L138" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="M138" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N138" s="10" t="str">
         <f t="shared" si="28"/>
@@ -9676,22 +9685,22 @@
         <v>135：阿部花音</v>
       </c>
     </row>
-    <row r="139" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A139" s="5">
         <f t="shared" si="24"/>
         <v>136</v>
       </c>
       <c r="B139" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F139" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E139,TankaData[コース],0)),0)</f>
@@ -9717,10 +9726,10 @@
         <v>31020</v>
       </c>
       <c r="L139" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="M139" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N139" s="10" t="str">
         <f t="shared" si="28"/>
@@ -9731,22 +9740,22 @@
         <v>136：近藤大和</v>
       </c>
     </row>
-    <row r="140" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A140" s="5">
         <f t="shared" si="24"/>
         <v>137</v>
       </c>
       <c r="B140" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F140" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E140,TankaData[コース],0)),0)</f>
@@ -9772,10 +9781,10 @@
         <v>40260</v>
       </c>
       <c r="L140" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M140" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N140" s="10" t="str">
         <f t="shared" si="28"/>
@@ -9786,22 +9795,22 @@
         <v>137：田村陽向</v>
       </c>
     </row>
-    <row r="141" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A141" s="5">
         <f t="shared" si="24"/>
         <v>138</v>
       </c>
       <c r="B141" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F141" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E141,TankaData[コース],0)),0)</f>
@@ -9827,10 +9836,10 @@
         <v>31020</v>
       </c>
       <c r="L141" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="M141" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N141" s="10" t="str">
         <f t="shared" si="28"/>
@@ -9841,22 +9850,22 @@
         <v>138：岡本美結</v>
       </c>
     </row>
-    <row r="142" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A142" s="5">
         <f t="shared" si="24"/>
         <v>139</v>
       </c>
       <c r="B142" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F142" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E142,TankaData[コース],0)),0)</f>
@@ -9882,10 +9891,10 @@
         <v>37950</v>
       </c>
       <c r="L142" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="M142" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N142" s="10" t="str">
         <f t="shared" si="28"/>
@@ -9896,22 +9905,22 @@
         <v>139：森花音</v>
       </c>
     </row>
-    <row r="143" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A143" s="5">
         <f t="shared" si="24"/>
         <v>140</v>
       </c>
       <c r="B143" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F143" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E143,TankaData[コース],0)),0)</f>
@@ -9937,10 +9946,10 @@
         <v>52800</v>
       </c>
       <c r="L143" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="M143" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N143" s="10" t="str">
         <f t="shared" si="28"/>
@@ -9951,22 +9960,22 @@
         <v>140：太田優奈</v>
       </c>
     </row>
-    <row r="144" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A144" s="5">
         <f t="shared" si="24"/>
         <v>141</v>
       </c>
       <c r="B144" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F144" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E144,TankaData[コース],0)),0)</f>
@@ -9992,10 +10001,10 @@
         <v>31020</v>
       </c>
       <c r="L144" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="M144" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N144" s="10" t="str">
         <f t="shared" si="28"/>
@@ -10006,22 +10015,22 @@
         <v>141：山本美月</v>
       </c>
     </row>
-    <row r="145" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A145" s="5">
         <f t="shared" si="24"/>
         <v>142</v>
       </c>
       <c r="B145" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F145" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E145,TankaData[コース],0)),0)</f>
@@ -10047,10 +10056,10 @@
         <v>78100</v>
       </c>
       <c r="L145" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="M145" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N145" s="10" t="str">
         <f t="shared" si="28"/>
@@ -10061,22 +10070,22 @@
         <v>142：木村心春</v>
       </c>
     </row>
-    <row r="146" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A146" s="5">
         <f t="shared" si="24"/>
         <v>143</v>
       </c>
       <c r="B146" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F146" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E146,TankaData[コース],0)),0)</f>
@@ -10102,10 +10111,10 @@
         <v>37950</v>
       </c>
       <c r="L146" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="M146" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N146" s="10" t="str">
         <f t="shared" si="28"/>
@@ -10116,22 +10125,22 @@
         <v>143：山口朝陽</v>
       </c>
     </row>
-    <row r="147" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A147" s="5">
         <f t="shared" si="24"/>
         <v>144</v>
       </c>
       <c r="B147" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F147" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E147,TankaData[コース],0)),0)</f>
@@ -10157,10 +10166,10 @@
         <v>78100</v>
       </c>
       <c r="L147" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="M147" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N147" s="10" t="str">
         <f t="shared" si="28"/>
@@ -10171,22 +10180,22 @@
         <v>144：伊藤楓</v>
       </c>
     </row>
-    <row r="148" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A148" s="5">
         <f t="shared" si="24"/>
         <v>145</v>
       </c>
       <c r="B148" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F148" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E148,TankaData[コース],0)),0)</f>
@@ -10212,10 +10221,10 @@
         <v>95700</v>
       </c>
       <c r="L148" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="M148" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N148" s="10" t="str">
         <f t="shared" si="28"/>
@@ -10226,22 +10235,22 @@
         <v>145：斎藤一輝</v>
       </c>
     </row>
-    <row r="149" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A149" s="5">
         <f t="shared" si="24"/>
         <v>146</v>
       </c>
       <c r="B149" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F149" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E149,TankaData[コース],0)),0)</f>
@@ -10267,10 +10276,10 @@
         <v>12540</v>
       </c>
       <c r="L149" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="M149" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N149" s="10" t="str">
         <f t="shared" si="28"/>
@@ -10281,22 +10290,22 @@
         <v>146：遠藤大和</v>
       </c>
     </row>
-    <row r="150" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A150" s="5">
         <f t="shared" si="24"/>
         <v>147</v>
       </c>
       <c r="B150" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F150" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E150,TankaData[コース],0)),0)</f>
@@ -10322,10 +10331,10 @@
         <v>59950</v>
       </c>
       <c r="L150" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="M150" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N150" s="10" t="str">
         <f t="shared" si="28"/>
@@ -10336,22 +10345,22 @@
         <v>147：金子心春</v>
       </c>
     </row>
-    <row r="151" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A151" s="5">
         <f t="shared" si="24"/>
         <v>148</v>
       </c>
       <c r="B151" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F151" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E151,TankaData[コース],0)),0)</f>
@@ -10377,10 +10386,10 @@
         <v>12540</v>
       </c>
       <c r="L151" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="M151" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N151" s="10" t="str">
         <f t="shared" si="28"/>
@@ -10391,22 +10400,22 @@
         <v>148：田中美桜</v>
       </c>
     </row>
-    <row r="152" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A152" s="5">
         <f t="shared" si="24"/>
         <v>149</v>
       </c>
       <c r="B152" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F152" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E152,TankaData[コース],0)),0)</f>
@@ -10432,10 +10441,10 @@
         <v>59950</v>
       </c>
       <c r="L152" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="M152" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N152" s="10" t="str">
         <f t="shared" si="28"/>
@@ -10446,22 +10455,22 @@
         <v>149：小野湊</v>
       </c>
     </row>
-    <row r="153" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A153" s="5">
         <f t="shared" si="24"/>
         <v>150</v>
       </c>
       <c r="B153" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F153" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E153,TankaData[コース],0)),0)</f>
@@ -10487,10 +10496,10 @@
         <v>48950</v>
       </c>
       <c r="L153" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="M153" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N153" s="10" t="str">
         <f t="shared" si="28"/>
@@ -10501,22 +10510,22 @@
         <v>150：石井琴音</v>
       </c>
     </row>
-    <row r="154" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A154" s="5">
         <f t="shared" si="24"/>
         <v>151</v>
       </c>
       <c r="B154" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F154" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E154,TankaData[コース],0)),0)</f>
@@ -10542,10 +10551,10 @@
         <v>25300</v>
       </c>
       <c r="L154" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="M154" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N154" s="10" t="str">
         <f t="shared" si="28"/>
@@ -10556,22 +10565,22 @@
         <v>151：近藤大翔</v>
       </c>
     </row>
-    <row r="155" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A155" s="5">
         <f t="shared" si="24"/>
         <v>152</v>
       </c>
       <c r="B155" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F155" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E155,TankaData[コース],0)),0)</f>
@@ -10597,10 +10606,10 @@
         <v>52800</v>
       </c>
       <c r="L155" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="M155" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N155" s="10" t="str">
         <f t="shared" si="28"/>
@@ -10611,22 +10620,22 @@
         <v>152：佐藤悠真</v>
       </c>
     </row>
-    <row r="156" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A156" s="5">
         <f t="shared" si="24"/>
         <v>153</v>
       </c>
       <c r="B156" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F156" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E156,TankaData[コース],0)),0)</f>
@@ -10652,10 +10661,10 @@
         <v>95700</v>
       </c>
       <c r="L156" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="M156" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N156" s="10" t="str">
         <f t="shared" si="28"/>
@@ -10666,22 +10675,22 @@
         <v>153：長谷川美月</v>
       </c>
     </row>
-    <row r="157" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A157" s="5">
         <f t="shared" si="24"/>
         <v>154</v>
       </c>
       <c r="B157" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F157" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E157,TankaData[コース],0)),0)</f>
@@ -10707,10 +10716,10 @@
         <v>42900</v>
       </c>
       <c r="L157" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="M157" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N157" s="10" t="str">
         <f t="shared" si="28"/>
@@ -10721,22 +10730,22 @@
         <v>154：近藤拓也</v>
       </c>
     </row>
-    <row r="158" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A158" s="5">
         <f t="shared" si="24"/>
         <v>155</v>
       </c>
       <c r="B158" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F158" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E158,TankaData[コース],0)),0)</f>
@@ -10762,10 +10771,10 @@
         <v>12540</v>
       </c>
       <c r="L158" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="M158" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N158" s="10" t="str">
         <f t="shared" si="28"/>
@@ -10776,22 +10785,22 @@
         <v>155：中村駿</v>
       </c>
     </row>
-    <row r="159" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A159" s="5">
         <f t="shared" si="24"/>
         <v>156</v>
       </c>
       <c r="B159" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F159" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E159,TankaData[コース],0)),0)</f>
@@ -10817,10 +10826,10 @@
         <v>31020</v>
       </c>
       <c r="L159" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="M159" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N159" s="10" t="str">
         <f t="shared" si="28"/>
@@ -10831,22 +10840,22 @@
         <v>156：伊藤煌</v>
       </c>
     </row>
-    <row r="160" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A160" s="5">
         <f t="shared" si="24"/>
         <v>157</v>
       </c>
       <c r="B160" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F160" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E160,TankaData[コース],0)),0)</f>
@@ -10872,10 +10881,10 @@
         <v>48950</v>
       </c>
       <c r="L160" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="M160" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N160" s="10" t="str">
         <f t="shared" si="28"/>
@@ -10886,22 +10895,22 @@
         <v>157：金子美桜</v>
       </c>
     </row>
-    <row r="161" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A161" s="5">
         <f t="shared" si="24"/>
         <v>158</v>
       </c>
       <c r="B161" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F161" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E161,TankaData[コース],0)),0)</f>
@@ -10927,10 +10936,10 @@
         <v>21780</v>
       </c>
       <c r="L161" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="M161" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N161" s="10" t="str">
         <f t="shared" si="28"/>
@@ -10941,22 +10950,22 @@
         <v>158：池田彩花</v>
       </c>
     </row>
-    <row r="162" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A162" s="5">
         <f t="shared" si="24"/>
         <v>159</v>
       </c>
       <c r="B162" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F162" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E162,TankaData[コース],0)),0)</f>
@@ -10982,10 +10991,10 @@
         <v>68200</v>
       </c>
       <c r="L162" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="M162" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N162" s="10" t="str">
         <f t="shared" si="28"/>
@@ -10996,22 +11005,22 @@
         <v>159：岡本悠斗</v>
       </c>
     </row>
-    <row r="163" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A163" s="5">
         <f t="shared" si="24"/>
         <v>160</v>
       </c>
       <c r="B163" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F163" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E163,TankaData[コース],0)),0)</f>
@@ -11037,10 +11046,10 @@
         <v>22000</v>
       </c>
       <c r="L163" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="M163" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N163" s="10" t="str">
         <f t="shared" si="28"/>
@@ -11051,22 +11060,22 @@
         <v>160：加藤湊</v>
       </c>
     </row>
-    <row r="164" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A164" s="5">
         <f t="shared" ref="A164:A183" si="30">ROW()-3</f>
         <v>161</v>
       </c>
       <c r="B164" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F164" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E164,TankaData[コース],0)),0)</f>
@@ -11092,10 +11101,10 @@
         <v>31020</v>
       </c>
       <c r="L164" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="M164" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N164" s="10" t="str">
         <f t="shared" ref="N164:N183" si="34">"教室："&amp;C164&amp;"／コース："&amp;E164&amp;"／コマ数："&amp;H164&amp;"コマ／授業料："&amp;TEXT(J164,"#,##0")&amp;"円／教材費："&amp;TEXT(I164,"#,##0")&amp;"円／消費税："&amp;TEXT(ROUND((J164+I164)*0.1,0),"#,##0")&amp;"円／請求額："&amp;TEXT(K164,"#,##0")&amp;"円"</f>
@@ -11106,22 +11115,22 @@
         <v>161：松本結翔</v>
       </c>
     </row>
-    <row r="165" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A165" s="5">
         <f t="shared" si="30"/>
         <v>162</v>
       </c>
       <c r="B165" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F165" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E165,TankaData[コース],0)),0)</f>
@@ -11147,10 +11156,10 @@
         <v>15950</v>
       </c>
       <c r="L165" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="M165" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N165" s="10" t="str">
         <f t="shared" si="34"/>
@@ -11161,22 +11170,22 @@
         <v>162：山崎美咲</v>
       </c>
     </row>
-    <row r="166" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A166" s="5">
         <f t="shared" si="30"/>
         <v>163</v>
       </c>
       <c r="B166" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F166" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E166,TankaData[コース],0)),0)</f>
@@ -11202,10 +11211,10 @@
         <v>59950</v>
       </c>
       <c r="L166" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="M166" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N166" s="10" t="str">
         <f t="shared" si="34"/>
@@ -11216,22 +11225,22 @@
         <v>163：山口大翔</v>
       </c>
     </row>
-    <row r="167" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A167" s="5">
         <f t="shared" si="30"/>
         <v>164</v>
       </c>
       <c r="B167" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F167" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E167,TankaData[コース],0)),0)</f>
@@ -11257,10 +11266,10 @@
         <v>68200</v>
       </c>
       <c r="L167" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="M167" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N167" s="10" t="str">
         <f t="shared" si="34"/>
@@ -11271,22 +11280,22 @@
         <v>164：鈴木遥</v>
       </c>
     </row>
-    <row r="168" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A168" s="5">
         <f t="shared" si="30"/>
         <v>165</v>
       </c>
       <c r="B168" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F168" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E168,TankaData[コース],0)),0)</f>
@@ -11312,10 +11321,10 @@
         <v>31020</v>
       </c>
       <c r="L168" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="M168" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N168" s="10" t="str">
         <f t="shared" si="34"/>
@@ -11326,22 +11335,22 @@
         <v>165：小野朝陽</v>
       </c>
     </row>
-    <row r="169" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A169" s="5">
         <f t="shared" si="30"/>
         <v>166</v>
       </c>
       <c r="B169" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F169" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E169,TankaData[コース],0)),0)</f>
@@ -11367,10 +11376,10 @@
         <v>40260</v>
       </c>
       <c r="L169" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="M169" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N169" s="10" t="str">
         <f t="shared" si="34"/>
@@ -11381,22 +11390,22 @@
         <v>166：山崎紬</v>
       </c>
     </row>
-    <row r="170" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A170" s="5">
         <f t="shared" si="30"/>
         <v>167</v>
       </c>
       <c r="B170" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F170" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E170,TankaData[コース],0)),0)</f>
@@ -11422,10 +11431,10 @@
         <v>37400</v>
       </c>
       <c r="L170" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="M170" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N170" s="10" t="str">
         <f t="shared" si="34"/>
@@ -11436,22 +11445,22 @@
         <v>167：岡田葵</v>
       </c>
     </row>
-    <row r="171" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A171" s="5">
         <f t="shared" si="30"/>
         <v>168</v>
       </c>
       <c r="B171" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F171" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E171,TankaData[コース],0)),0)</f>
@@ -11477,10 +11486,10 @@
         <v>68200</v>
       </c>
       <c r="L171" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="M171" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N171" s="10" t="str">
         <f t="shared" si="34"/>
@@ -11491,22 +11500,22 @@
         <v>168：田村琴音</v>
       </c>
     </row>
-    <row r="172" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A172" s="5">
         <f t="shared" si="30"/>
         <v>169</v>
       </c>
       <c r="B172" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F172" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E172,TankaData[コース],0)),0)</f>
@@ -11532,10 +11541,10 @@
         <v>48950</v>
       </c>
       <c r="L172" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="M172" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N172" s="10" t="str">
         <f t="shared" si="34"/>
@@ -11546,22 +11555,22 @@
         <v>169：竹内楓</v>
       </c>
     </row>
-    <row r="173" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A173" s="5">
         <f t="shared" si="30"/>
         <v>170</v>
       </c>
       <c r="B173" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F173" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E173,TankaData[コース],0)),0)</f>
@@ -11587,10 +11596,10 @@
         <v>21780</v>
       </c>
       <c r="L173" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="M173" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N173" s="10" t="str">
         <f t="shared" si="34"/>
@@ -11601,22 +11610,22 @@
         <v>170：藤井遥</v>
       </c>
     </row>
-    <row r="174" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A174" s="5">
         <f t="shared" si="30"/>
         <v>171</v>
       </c>
       <c r="B174" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F174" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E174,TankaData[コース],0)),0)</f>
@@ -11642,10 +11651,10 @@
         <v>42900</v>
       </c>
       <c r="L174" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="M174" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N174" s="10" t="str">
         <f t="shared" si="34"/>
@@ -11656,22 +11665,22 @@
         <v>171：長谷川悠真</v>
       </c>
     </row>
-    <row r="175" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A175" s="5">
         <f t="shared" si="30"/>
         <v>172</v>
       </c>
       <c r="B175" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F175" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E175,TankaData[コース],0)),0)</f>
@@ -11697,10 +11706,10 @@
         <v>15950</v>
       </c>
       <c r="L175" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="M175" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N175" s="10" t="str">
         <f t="shared" si="34"/>
@@ -11711,22 +11720,22 @@
         <v>172：林海斗</v>
       </c>
     </row>
-    <row r="176" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A176" s="5">
         <f t="shared" si="30"/>
         <v>173</v>
       </c>
       <c r="B176" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F176" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E176,TankaData[コース],0)),0)</f>
@@ -11752,10 +11761,10 @@
         <v>95700</v>
       </c>
       <c r="L176" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="M176" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N176" s="10" t="str">
         <f t="shared" si="34"/>
@@ -11766,22 +11775,22 @@
         <v>173：伊藤萌</v>
       </c>
     </row>
-    <row r="177" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A177" s="5">
         <f t="shared" si="30"/>
         <v>174</v>
       </c>
       <c r="B177" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F177" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E177,TankaData[コース],0)),0)</f>
@@ -11807,10 +11816,10 @@
         <v>42900</v>
       </c>
       <c r="L177" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="M177" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N177" s="10" t="str">
         <f t="shared" si="34"/>
@@ -11821,22 +11830,22 @@
         <v>174：近藤蓮</v>
       </c>
     </row>
-    <row r="178" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A178" s="5">
         <f t="shared" si="30"/>
         <v>175</v>
       </c>
       <c r="B178" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F178" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E178,TankaData[コース],0)),0)</f>
@@ -11862,10 +11871,10 @@
         <v>22000</v>
       </c>
       <c r="L178" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="M178" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N178" s="10" t="str">
         <f t="shared" si="34"/>
@@ -11876,22 +11885,22 @@
         <v>175：井上尊</v>
       </c>
     </row>
-    <row r="179" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A179" s="5">
         <f t="shared" si="30"/>
         <v>176</v>
       </c>
       <c r="B179" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F179" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E179,TankaData[コース],0)),0)</f>
@@ -11917,10 +11926,10 @@
         <v>37950</v>
       </c>
       <c r="L179" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="M179" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N179" s="10" t="str">
         <f t="shared" si="34"/>
@@ -11931,22 +11940,22 @@
         <v>176：西村尊</v>
       </c>
     </row>
-    <row r="180" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A180" s="5">
         <f t="shared" si="30"/>
         <v>177</v>
       </c>
       <c r="B180" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F180" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E180,TankaData[コース],0)),0)</f>
@@ -11972,10 +11981,10 @@
         <v>60500</v>
       </c>
       <c r="L180" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="M180" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N180" s="10" t="str">
         <f t="shared" si="34"/>
@@ -11986,22 +11995,22 @@
         <v>177：藤井美桜</v>
       </c>
     </row>
-    <row r="181" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A181" s="5">
         <f t="shared" si="30"/>
         <v>178</v>
       </c>
       <c r="B181" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F181" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E181,TankaData[コース],0)),0)</f>
@@ -12027,10 +12036,10 @@
         <v>31020</v>
       </c>
       <c r="L181" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="M181" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N181" s="10" t="str">
         <f t="shared" si="34"/>
@@ -12041,22 +12050,22 @@
         <v>178：山口美桜</v>
       </c>
     </row>
-    <row r="182" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A182" s="5">
         <f t="shared" si="30"/>
         <v>179</v>
       </c>
       <c r="B182" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F182" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E182,TankaData[コース],0)),0)</f>
@@ -12082,10 +12091,10 @@
         <v>95700</v>
       </c>
       <c r="L182" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="M182" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N182" s="10" t="str">
         <f t="shared" si="34"/>
@@ -12096,22 +12105,22 @@
         <v>179：竹内花音</v>
       </c>
     </row>
-    <row r="183" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A183" s="5">
         <f t="shared" si="30"/>
         <v>180</v>
       </c>
       <c r="B183" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F183" s="6">
         <f>IFERROR(INDEX(TankaData[1コマ単価],MATCH(E183,TankaData[コース],0)),0)</f>
@@ -12137,10 +12146,10 @@
         <v>52800</v>
       </c>
       <c r="L183" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="M183" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N183" s="10" t="str">
         <f t="shared" si="34"/>
@@ -12151,9 +12160,9 @@
         <v>180：前田葵</v>
       </c>
     </row>
-    <row r="184" spans="1:15" collapsed="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A184" s="45" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B184" s="46"/>
       <c r="C184" s="46"/>
@@ -12416,14 +12425,14 @@
         <v>46252</v>
       </c>
       <c r="F1" s="23"/>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="29" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="23"/>
       <c r="J1" s="23"/>
       <c r="K1" s="23"/>
       <c r="L1" s="23"/>
-      <c r="N1" s="29" t="s">
+      <c r="N1" s="28" t="s">
         <v>3</v>
       </c>
       <c r="O1" s="23"/>
@@ -12497,10 +12506,15 @@
       <c r="J5" s="41"/>
       <c r="K5" s="42"/>
       <c r="L5" s="39"/>
+      <c r="N5" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
     </row>
     <row r="6" spans="1:16" ht="15.5" x14ac:dyDescent="0.25">
       <c r="H6" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J6" s="24" t="str">
         <f>IF($J$4&lt;&gt;"",IF(COUNTIF(SeikyuData[No],$J$4)=0,"⚠ 該当するNoがありません",$J$4),IF($J$5&lt;&gt;"",VALUE(LEFT($J$5,FIND("：",$J$5)-1)),""))</f>
@@ -12508,13 +12522,18 @@
       </c>
       <c r="K6" s="23"/>
       <c r="L6" s="23"/>
+      <c r="N6" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
     </row>
     <row r="7" spans="1:16" ht="15.5" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J7" s="24" t="str">
         <f>IFERROR(INDEX(SeikyuData[生徒名],MATCH($J$6,SeikyuData[No],0)),"")</f>
@@ -12522,10 +12541,15 @@
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="23"/>
+      <c r="N7" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
     </row>
     <row r="8" spans="1:16" ht="14" x14ac:dyDescent="0.2">
       <c r="A8" s="19" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C8" s="23" t="str">
         <f>IFERROR(INDEX(SeikyuData[教室],MATCH($J$6,SeikyuData[No],0)),"")</f>
@@ -12534,12 +12558,15 @@
       <c r="D8" s="23"/>
       <c r="E8" s="23"/>
       <c r="H8" s="18" t="s">
-        <v>17</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="19" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C9" s="23" t="str">
         <f>IFERROR(INDEX(SeikyuData[学年],MATCH($J$6,SeikyuData[No],0)),"")</f>
@@ -12548,7 +12575,7 @@
       <c r="D9" s="23"/>
       <c r="E9" s="23"/>
       <c r="H9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J9" s="23" t="str">
         <f>IFERROR(INDEX(SeikyuData[保護者メール],MATCH($J$6,SeikyuData[No],0)),"")</f>
@@ -12559,7 +12586,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="19" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C10" s="23" t="str">
         <f>IFERROR(INDEX(SeikyuData[コース],MATCH($J$6,SeikyuData[No],0)),"")</f>
@@ -12568,7 +12595,7 @@
       <c r="D10" s="23"/>
       <c r="E10" s="23"/>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J10" s="23" t="str">
         <f>$J$7 &amp; "様 2026年8月分請求のお知らせ"</f>
@@ -12579,7 +12606,7 @@
     </row>
     <row r="11" spans="1:16" ht="14" x14ac:dyDescent="0.2">
       <c r="A11" s="19" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C11" s="22" t="str">
         <f>IFERROR(INDEX(SeikyuData[1コマ単価],MATCH($J$6,SeikyuData[No],0)),"")</f>
@@ -12596,7 +12623,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="19" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C12" s="31" t="str">
         <f>IFERROR(INDEX(SeikyuData[週コマ数],MATCH($J$6,SeikyuData[No],0)),"")</f>
@@ -12605,14 +12632,14 @@
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
       <c r="J12" s="32" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="23"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="19" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C13" s="31" t="str">
         <f>IFERROR(INDEX(SeikyuData[コマ数],MATCH($J$6,SeikyuData[No],0)),"")</f>
@@ -12623,7 +12650,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="19" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C14" s="22" t="str">
         <f>IFERROR(INDEX(SeikyuData[教材費],MATCH($J$6,SeikyuData[No],0)),"")</f>
@@ -12632,12 +12659,12 @@
       <c r="D14" s="23"/>
       <c r="E14" s="23"/>
       <c r="H14" s="16" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="19" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C15" s="22" t="str">
         <f>IFERROR(INDEX(SeikyuData[授業料],MATCH($J$6,SeikyuData[No],0)),"")</f>
@@ -12656,7 +12683,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="19" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C16" s="22" t="str">
         <f>IFERROR(ROUND((INDEX(SeikyuData[授業料],MATCH($J$6,SeikyuData[No],0))+INDEX(SeikyuData[教材費],MATCH($J$6,SeikyuData[No],0)))*0.1,0),"")</f>
@@ -12672,7 +12699,7 @@
     </row>
     <row r="17" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="35" t="str">
@@ -12697,10 +12724,10 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="20" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B19" s="30" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C19" s="23"/>
       <c r="D19" s="23"/>
@@ -12714,7 +12741,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B20" s="44">
         <f ca="1">TODAY()+14</f>
@@ -12732,7 +12759,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="30" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B21" s="23"/>
       <c r="C21" s="23"/>
@@ -12754,13 +12781,13 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="17" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F23" s="23"/>
       <c r="H23" s="23"/>
@@ -12820,14 +12847,14 @@
     </row>
     <row r="32" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="J32" s="33" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K32" s="23"/>
       <c r="L32" s="23"/>
     </row>
     <row r="33" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J33" s="32" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K33" s="23"/>
       <c r="L33" s="23"/>
@@ -12839,18 +12866,18 @@
     </row>
     <row r="35" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J35" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K35" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L35" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J36" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K36" s="21">
         <v>4000</v>
@@ -12861,7 +12888,7 @@
     </row>
     <row r="37" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J37" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K37" s="21">
         <v>3500</v>
@@ -12872,7 +12899,7 @@
     </row>
     <row r="38" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J38" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K38" s="21">
         <v>2500</v>
@@ -12883,7 +12910,7 @@
     </row>
     <row r="39" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J39" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K39" s="21">
         <v>2100</v>
@@ -12893,47 +12920,51 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="38">
     <mergeCell ref="J33:L34"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="C11:E11"/>
+    <mergeCell ref="N7:P8"/>
     <mergeCell ref="J32:L32"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A5:F5"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C17:E17"/>
-    <mergeCell ref="A4:F4"/>
     <mergeCell ref="J12:L12"/>
-    <mergeCell ref="J4:K4"/>
     <mergeCell ref="C13:E13"/>
-    <mergeCell ref="E2:F2"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="C15:E15"/>
-    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="C10:E10"/>
     <mergeCell ref="H1:L1"/>
     <mergeCell ref="N1:P1"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="C12:E12"/>
     <mergeCell ref="J11:L11"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="N6:P6"/>
     <mergeCell ref="N3:P4"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="J5:L5"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="C10:E10"/>
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="H15:L30"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="C9:E9"/>
+    <mergeCell ref="N5:P5"/>
     <mergeCell ref="E23:F23"/>
   </mergeCells>
   <phoneticPr fontId="22"/>
   <hyperlinks>
     <hyperlink ref="N2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
     <hyperlink ref="H3" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="N6" location="'月末請求一覧'!G4" display="📋 一覧表を開く（週コマ数を編集）" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/一覧表.xlsx
+++ b/一覧表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5da398a782259f2f/ドキュメント/Claude/Projects/演習問題/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_8E1FB7C76C0B3F77EAAFFC8136C04249F91CF42A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_B2A5B6C76CFB2B6D48E346803D893EAAF6D455B6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3550" yWindow="2490" windowWidth="13430" windowHeight="7270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="280" yWindow="2650" windowWidth="13430" windowHeight="7270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="月末請求一覧" sheetId="1" r:id="rId1"/>
@@ -216,7 +216,8 @@
     <t>選択中のNo</t>
   </si>
   <si>
-    <t>📋 一覧表を開く（週コマ数を編集）</t>
+    <t>📋 一覧表を開く
+（週コマ数を編集）</t>
   </si>
   <si>
     <t>ご請求内容</t>
@@ -225,13 +226,13 @@
     <t>選択中の生徒名</t>
   </si>
   <si>
+    <t>教室</t>
+  </si>
+  <si>
+    <t>メールで送る</t>
+  </si>
+  <si>
     <t>「月末請求一覧」タブに切り替わります。黄色いセル（週コマ数）に数字を入力してください。</t>
-  </si>
-  <si>
-    <t>教室</t>
-  </si>
-  <si>
-    <t>メールで送る</t>
   </si>
   <si>
     <t>学年</t>
@@ -1681,7 +1682,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1701,6 +1702,72 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF2F7D68"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF2F7D68"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF2F7D68"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF2F7D68"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF2F7D68"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF2F7D68"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF2F7D68"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF2F7D68"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF2F7D68"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF2F7D68"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF2F7D68"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF2F7D68"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1747,7 +1814,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1784,6 +1851,14 @@
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1802,15 +1877,15 @@
     <xf numFmtId="3" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2180,7 +2255,7 @@
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="47">
+      <c r="B1" s="53">
         <f>SUM(SeikyuData[請求額(税込)])</f>
         <v>8318530</v>
       </c>
@@ -2196,7 +2271,7 @@
       <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="54" t="s">
         <v>49</v>
       </c>
       <c r="B2" s="23"/>
@@ -2221,7 +2296,7 @@
         <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>21</v>
@@ -12161,13 +12236,13 @@
       </c>
     </row>
     <row r="184" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A184" s="45" t="s">
+      <c r="A184" s="51" t="s">
         <v>431</v>
       </c>
-      <c r="B184" s="46"/>
-      <c r="C184" s="46"/>
-      <c r="D184" s="46"/>
-      <c r="E184" s="46"/>
+      <c r="B184" s="52"/>
+      <c r="C184" s="52"/>
+      <c r="D184" s="52"/>
+      <c r="E184" s="52"/>
       <c r="F184" s="11"/>
       <c r="G184" s="11"/>
       <c r="H184" s="12">
@@ -12412,7 +12487,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.4">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="23"/>
@@ -12420,19 +12495,19 @@
       <c r="D1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="34">
+      <c r="E1" s="40">
         <f ca="1">TODAY()</f>
         <v>46252</v>
       </c>
       <c r="F1" s="23"/>
-      <c r="H1" s="29" t="s">
+      <c r="H1" s="35" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="23"/>
       <c r="J1" s="23"/>
       <c r="K1" s="23"/>
       <c r="L1" s="23"/>
-      <c r="N1" s="28" t="s">
+      <c r="N1" s="34" t="s">
         <v>3</v>
       </c>
       <c r="O1" s="23"/>
@@ -12445,7 +12520,7 @@
       <c r="D2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="40" t="str">
+      <c r="E2" s="46" t="str">
         <f>IFERROR(INDEX(SeikyuData[No],MATCH($J$6,SeikyuData[No],0)),"")</f>
         <v/>
       </c>
@@ -12453,27 +12528,27 @@
       <c r="H2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="25" t="s">
+      <c r="N2" s="31" t="s">
         <v>7</v>
       </c>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="H3" s="27" t="s">
+      <c r="H3" s="33" t="s">
         <v>8</v>
       </c>
       <c r="I3" s="23"/>
       <c r="J3" s="23"/>
       <c r="K3" s="23"/>
-      <c r="N3" s="32" t="s">
+      <c r="N3" s="38" t="s">
         <v>9</v>
       </c>
       <c r="O3" s="23"/>
       <c r="P3" s="23"/>
     </row>
     <row r="4" spans="1:16" ht="19" x14ac:dyDescent="0.3">
-      <c r="A4" s="37" t="str">
+      <c r="A4" s="43" t="str">
         <f>IF($J$6="","（右の操作パネルでNoか生徒名を選択してください）",$J$7&amp;"　様")</f>
         <v>（右の操作パネルでNoか生徒名を選択してください）</v>
       </c>
@@ -12485,14 +12560,14 @@
       <c r="H4" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="45"/>
       <c r="N4" s="23"/>
       <c r="O4" s="23"/>
       <c r="P4" s="23"/>
     </row>
     <row r="5" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="36" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="23"/>
@@ -12503,53 +12578,51 @@
       <c r="H5" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="39"/>
-      <c r="N5" s="28" t="s">
+      <c r="J5" s="47"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="45"/>
+      <c r="N5" s="34" t="s">
         <v>13</v>
       </c>
       <c r="O5" s="23"/>
       <c r="P5" s="23"/>
     </row>
-    <row r="6" spans="1:16" ht="15.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H6" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="J6" s="24" t="str">
+      <c r="J6" s="30" t="str">
         <f>IF($J$4&lt;&gt;"",IF(COUNTIF(SeikyuData[No],$J$4)=0,"⚠ 該当するNoがありません",$J$4),IF($J$5&lt;&gt;"",VALUE(LEFT($J$5,FIND("：",$J$5)-1)),""))</f>
         <v/>
       </c>
       <c r="K6" s="23"/>
       <c r="L6" s="23"/>
-      <c r="N6" s="25" t="s">
+      <c r="N6" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-    </row>
-    <row r="7" spans="1:16" ht="15.5" x14ac:dyDescent="0.25">
+      <c r="O6" s="25"/>
+      <c r="P6" s="26"/>
+    </row>
+    <row r="7" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>16</v>
       </c>
       <c r="H7" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="24" t="str">
+      <c r="J7" s="30" t="str">
         <f>IFERROR(INDEX(SeikyuData[生徒名],MATCH($J$6,SeikyuData[No],0)),"")</f>
         <v/>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="23"/>
-      <c r="N7" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="29"/>
     </row>
     <row r="8" spans="1:16" ht="14" x14ac:dyDescent="0.2">
       <c r="A8" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="23" t="str">
         <f>IFERROR(INDEX(SeikyuData[教室],MATCH($J$6,SeikyuData[No],0)),"")</f>
@@ -12558,9 +12631,11 @@
       <c r="D8" s="23"/>
       <c r="E8" s="23"/>
       <c r="H8" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="N8" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="N8" s="23"/>
       <c r="O8" s="23"/>
       <c r="P8" s="23"/>
     </row>
@@ -12583,6 +12658,9 @@
       </c>
       <c r="K9" s="23"/>
       <c r="L9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="19" t="s">
@@ -12614,7 +12692,7 @@
       </c>
       <c r="D11" s="23"/>
       <c r="E11" s="23"/>
-      <c r="J11" s="25" t="str">
+      <c r="J11" s="31" t="str">
         <f>IF($J$6="","",HYPERLINK("https://mail.google.com/mail/?view=cm&amp;fs=1&amp;to=" &amp; _xlfn.ENCODEURL(IFERROR(INDEX(SeikyuData[保護者メール],MATCH($J$6,SeikyuData[No],0)),"")) &amp; "&amp;su=" &amp; _xlfn.ENCODEURL($J$7 &amp; "様 2026年8月分請求のお知らせ"),"📧 Gmail作成画面を開く（宛先・件名 入力済み）"))</f>
         <v/>
       </c>
@@ -12625,13 +12703,13 @@
       <c r="A12" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="31" t="str">
+      <c r="C12" s="37" t="str">
         <f>IFERROR(INDEX(SeikyuData[週コマ数],MATCH($J$6,SeikyuData[No],0)),"")</f>
         <v/>
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
-      <c r="J12" s="32" t="s">
+      <c r="J12" s="38" t="s">
         <v>27</v>
       </c>
       <c r="K12" s="23"/>
@@ -12641,7 +12719,7 @@
       <c r="A13" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="31" t="str">
+      <c r="C13" s="37" t="str">
         <f>IFERROR(INDEX(SeikyuData[コマ数],MATCH($J$6,SeikyuData[No],0)),"")</f>
         <v/>
       </c>
@@ -12672,7 +12750,7 @@
       </c>
       <c r="D15" s="23"/>
       <c r="E15" s="23"/>
-      <c r="H15" s="26" t="str">
+      <c r="H15" s="32" t="str">
         <f ca="1">IF($J$6="","生徒名を選択すると本文が生成されます。",$J$7&amp;"様"&amp;CHAR(10)&amp;CHAR(10)&amp;"いつもお世話になっております。さくら学習塾です。"&amp;CHAR(10)&amp;"2026年8月分の請求内容は以下の通りです。"&amp;CHAR(10)&amp;CHAR(10)&amp;"教室：　"&amp;IFERROR(INDEX(SeikyuData[教室],MATCH($J$6,SeikyuData[No],0)),"")&amp;CHAR(10)&amp;"コース：　"&amp;IFERROR(INDEX(SeikyuData[コース],MATCH($J$6,SeikyuData[No],0)),"")&amp;CHAR(10)&amp;"コマ数：　"&amp;IFERROR(INDEX(SeikyuData[コマ数],MATCH($J$6,SeikyuData[No],0)),"")&amp;"コマ"&amp;CHAR(10)&amp;"授業料：　"&amp;TEXT(IFERROR(INDEX(SeikyuData[授業料],MATCH($J$6,SeikyuData[No],0)),""),"#,##0")&amp;"円"&amp;CHAR(10)&amp;"教材費：　"&amp;TEXT(IFERROR(INDEX(SeikyuData[教材費],MATCH($J$6,SeikyuData[No],0)),""),"#,##0")&amp;"円"&amp;CHAR(10)&amp;"消費税：　"&amp;TEXT(ROUND((IFERROR(INDEX(SeikyuData[授業料],MATCH($J$6,SeikyuData[No],0)),"")+IFERROR(INDEX(SeikyuData[教材費],MATCH($J$6,SeikyuData[No],0)),""))*0.1,0),"#,##0")&amp;"円"&amp;CHAR(10)&amp;"----------------"&amp;CHAR(10)&amp;"ご請求額：　"&amp;TEXT(IFERROR(INDEX(SeikyuData[請求額(税込)],MATCH($J$6,SeikyuData[No],0)),""),"#,##0")&amp;"円"&amp;CHAR(10)&amp;CHAR(10)&amp;"振込先：　〇〇銀行 〇〇支店　普通　1234567　口座名義：サクラガクシュウジュク"&amp;CHAR(10)&amp;"支払期日：　"&amp;TEXT(TODAY()+14,"yyyy/mm/dd")&amp;CHAR(10)&amp;CHAR(10)&amp;"お手数ですが、期日までにお振込みくださいますようお願いいたします。")</f>
         <v>生徒名を選択すると本文が生成されます。</v>
       </c>
@@ -12702,12 +12780,12 @@
         <v>33</v>
       </c>
       <c r="B17" s="2"/>
-      <c r="C17" s="35" t="str">
+      <c r="C17" s="41" t="str">
         <f>IFERROR(INDEX(SeikyuData[請求額(税込)],MATCH($J$6,SeikyuData[No],0)),"")</f>
         <v/>
       </c>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
       <c r="F17" s="2"/>
       <c r="H17" s="23"/>
       <c r="I17" s="23"/>
@@ -12726,7 +12804,7 @@
       <c r="A19" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="36" t="s">
         <v>35</v>
       </c>
       <c r="C19" s="23"/>
@@ -12743,7 +12821,7 @@
       <c r="A20" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="44">
+      <c r="B20" s="50">
         <f ca="1">TODAY()+14</f>
         <v>46266</v>
       </c>
@@ -12758,7 +12836,7 @@
       <c r="L20" s="23"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="36" t="s">
         <v>37</v>
       </c>
       <c r="B21" s="23"/>
@@ -12846,14 +12924,14 @@
       <c r="L30" s="23"/>
     </row>
     <row r="32" spans="1:12" ht="14" x14ac:dyDescent="0.2">
-      <c r="J32" s="33" t="s">
+      <c r="J32" s="39" t="s">
         <v>41</v>
       </c>
       <c r="K32" s="23"/>
       <c r="L32" s="23"/>
     </row>
     <row r="33" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J33" s="32" t="s">
+      <c r="J33" s="38" t="s">
         <v>42</v>
       </c>
       <c r="K33" s="23"/>
@@ -12924,34 +13002,34 @@
     <mergeCell ref="J33:L34"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="C11:E11"/>
-    <mergeCell ref="N7:P8"/>
     <mergeCell ref="J32:L32"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A5:F5"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C17:E17"/>
+    <mergeCell ref="A4:F4"/>
     <mergeCell ref="J12:L12"/>
+    <mergeCell ref="J4:K4"/>
     <mergeCell ref="C13:E13"/>
+    <mergeCell ref="E2:F2"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="J5:L5"/>
     <mergeCell ref="H1:L1"/>
     <mergeCell ref="N1:P1"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="C12:E12"/>
     <mergeCell ref="J11:L11"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="N6:P6"/>
     <mergeCell ref="N3:P4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="N8:P9"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="J10:L10"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="C10:E10"/>
     <mergeCell ref="C16:E16"/>
+    <mergeCell ref="N6:P7"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="H15:L30"/>
@@ -12964,7 +13042,7 @@
   <hyperlinks>
     <hyperlink ref="N2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
     <hyperlink ref="H3" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="N6" location="'月末請求一覧'!G4" display="📋 一覧表を開く（週コマ数を編集）" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="N6" location="'月末請求一覧'!G4" display="📋 一覧表を開く_x000a_（週コマ数を編集）" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
